--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.alpha.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,82 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -372,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -404,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -439,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,2374 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>4.1293409027811118E-2</v>
+        <v>0.03973040546005044</v>
       </c>
       <c r="C2">
-        <v>7.7161027205142729E-2</v>
+        <v>0.07427153771119521</v>
       </c>
       <c r="D2">
-        <v>0.1044630113776939</v>
+        <v>0.100041008761757</v>
       </c>
       <c r="E2">
-        <v>0.1085695763955727</v>
+        <v>0.1039197714386337</v>
       </c>
       <c r="F2">
-        <v>0.1686191406120876</v>
+        <v>0.1651278530609113</v>
       </c>
       <c r="G2">
-        <v>0.1600127646666577</v>
+        <v>0.1536940718332843</v>
       </c>
       <c r="H2">
-        <v>0.17137905802084721</v>
+        <v>0.1661361754323425</v>
       </c>
       <c r="I2">
-        <v>0.199600296927958</v>
+        <v>0.1934143912996075</v>
       </c>
       <c r="J2">
-        <v>0.23666924731407241</v>
+        <v>0.2368061540648556</v>
       </c>
       <c r="K2">
-        <v>0.27921020964305748</v>
+        <v>0.2796041920247191</v>
       </c>
       <c r="L2">
-        <v>0.28504868883544798</v>
+        <v>0.2876726830364041</v>
       </c>
       <c r="M2">
-        <v>0.33855470752049149</v>
+        <v>0.3427161571962502</v>
       </c>
       <c r="N2">
-        <v>0.3510930745187929</v>
+        <v>0.3546652476508932</v>
       </c>
       <c r="O2">
-        <v>0.39256786128791621</v>
+        <v>0.3962602282775642</v>
       </c>
       <c r="P2">
-        <v>0.38897272256569371</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3909918852779004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>5.0026638527342682E-2</v>
+        <v>0.04853158050493867</v>
       </c>
       <c r="C3">
-        <v>5.4386353714941882E-2</v>
+        <v>0.05160142424280179</v>
       </c>
       <c r="D3">
-        <v>9.3561522447773937E-2</v>
+        <v>0.09180381838711554</v>
       </c>
       <c r="E3">
-        <v>0.15841920862015421</v>
+        <v>0.1712583482043571</v>
       </c>
       <c r="F3">
-        <v>0.23233646199252031</v>
+        <v>0.2382326855596571</v>
       </c>
       <c r="G3">
-        <v>0.2617017241258402</v>
+        <v>0.2684542074698905</v>
       </c>
       <c r="H3">
-        <v>0.33283869511061998</v>
+        <v>0.3358472676706087</v>
       </c>
       <c r="I3">
-        <v>0.3868995279327338</v>
+        <v>0.3895004874767821</v>
       </c>
       <c r="J3">
-        <v>0.41972513361227082</v>
+        <v>0.4157323499797297</v>
       </c>
       <c r="K3">
-        <v>0.44084402153439728</v>
+        <v>0.4383140940677869</v>
       </c>
       <c r="L3">
-        <v>0.48791535690177129</v>
+        <v>0.4880769389738813</v>
       </c>
       <c r="M3">
-        <v>0.54094103841187857</v>
+        <v>0.5394951992493471</v>
       </c>
       <c r="N3">
-        <v>0.59684576195099937</v>
+        <v>0.5958687162210324</v>
       </c>
       <c r="O3">
-        <v>0.66633770394674552</v>
+        <v>0.6576958380425331</v>
       </c>
       <c r="P3">
-        <v>0.69908244085886029</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.6887702065823996</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.4683011500821981E-2</v>
+        <v>0.03724389129458505</v>
       </c>
       <c r="C4">
-        <v>6.5224843957689238E-2</v>
+        <v>0.07048287513836277</v>
       </c>
       <c r="D4">
-        <v>8.1669610429709827E-2</v>
+        <v>0.08543346611944502</v>
       </c>
       <c r="E4">
-        <v>0.14972574675472181</v>
+        <v>0.1580177749866928</v>
       </c>
       <c r="F4">
-        <v>0.15377847945221959</v>
+        <v>0.1611940115434754</v>
       </c>
       <c r="G4">
-        <v>0.19934368061165131</v>
+        <v>0.2127976745742741</v>
       </c>
       <c r="H4">
-        <v>0.21035843873823129</v>
+        <v>0.2212091919747212</v>
       </c>
       <c r="I4">
-        <v>0.25167808530443481</v>
+        <v>0.2618690928448231</v>
       </c>
       <c r="J4">
-        <v>0.27853390686627649</v>
+        <v>0.2890936104800714</v>
       </c>
       <c r="K4">
-        <v>0.36966279410218039</v>
+        <v>0.3804798141171343</v>
       </c>
       <c r="L4">
-        <v>0.41154821920007473</v>
+        <v>0.4212979275102951</v>
       </c>
       <c r="M4">
-        <v>0.43522624921982361</v>
+        <v>0.4464081092852262</v>
       </c>
       <c r="N4">
-        <v>0.44186683033821722</v>
+        <v>0.4478712395956488</v>
       </c>
       <c r="O4">
-        <v>0.47169742304814072</v>
+        <v>0.4727445387646012</v>
       </c>
       <c r="P4">
-        <v>0.5203317811927417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.5237543281662649</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>3.3388743855113652E-2</v>
+        <v>0.03523251527970223</v>
       </c>
       <c r="C5">
-        <v>7.2149897538017815E-2</v>
+        <v>0.0709691252211867</v>
       </c>
       <c r="D5">
-        <v>0.1017181353171123</v>
+        <v>0.09916776184024839</v>
       </c>
       <c r="E5">
-        <v>0.1774830329251337</v>
+        <v>0.1729847444118246</v>
       </c>
       <c r="F5">
-        <v>0.23155280266902281</v>
+        <v>0.2315595629742016</v>
       </c>
       <c r="G5">
-        <v>0.31515503102791342</v>
+        <v>0.3230525487928471</v>
       </c>
       <c r="H5">
-        <v>0.33924765467880519</v>
+        <v>0.3476053804466632</v>
       </c>
       <c r="I5">
-        <v>0.3483538313084934</v>
+        <v>0.3576970253169757</v>
       </c>
       <c r="J5">
-        <v>0.36108701606514959</v>
+        <v>0.3686228007975192</v>
       </c>
       <c r="K5">
-        <v>0.39762538638137801</v>
+        <v>0.4066644016296214</v>
       </c>
       <c r="L5">
-        <v>0.42385048446697698</v>
+        <v>0.4371293223339679</v>
       </c>
       <c r="M5">
-        <v>0.4624035887235286</v>
+        <v>0.4780055811310777</v>
       </c>
       <c r="N5">
-        <v>0.51766734802414605</v>
+        <v>0.5391385539487288</v>
       </c>
       <c r="O5">
-        <v>0.52547217006475722</v>
+        <v>0.5440760336142536</v>
       </c>
       <c r="P5">
-        <v>0.5625973504405648</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.5874833217325173</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>3.102205752984238E-2</v>
+        <v>0.03172043734825086</v>
       </c>
       <c r="C6">
-        <v>6.689804149784162E-2</v>
+        <v>0.06507633673295782</v>
       </c>
       <c r="D6">
-        <v>8.9307638680714729E-2</v>
+        <v>0.08921137398311496</v>
       </c>
       <c r="E6">
-        <v>0.24001130763509471</v>
+        <v>0.2399878810979922</v>
       </c>
       <c r="F6">
-        <v>0.2345476318345136</v>
+        <v>0.2390958090638362</v>
       </c>
       <c r="G6">
-        <v>0.30259927258747188</v>
+        <v>0.313877546547211</v>
       </c>
       <c r="H6">
-        <v>0.32057325589771768</v>
+        <v>0.3263084479419723</v>
       </c>
       <c r="I6">
-        <v>0.31355748424484059</v>
+        <v>0.3182127611213387</v>
       </c>
       <c r="J6">
-        <v>0.35058354110313511</v>
+        <v>0.3572308196138028</v>
       </c>
       <c r="K6">
-        <v>0.38078156947875091</v>
+        <v>0.3857784313392849</v>
       </c>
       <c r="L6">
-        <v>0.43156310975831652</v>
+        <v>0.4300664865544335</v>
       </c>
       <c r="M6">
-        <v>0.49227774815534731</v>
+        <v>0.489066306021916</v>
       </c>
       <c r="N6">
-        <v>0.53223559399384013</v>
+        <v>0.5346327155572879</v>
       </c>
       <c r="O6">
-        <v>0.54911251404019368</v>
+        <v>0.5523320264005198</v>
       </c>
       <c r="P6">
-        <v>0.53599189991313723</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.5395488832184715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3.7492992942061647E-2</v>
+        <v>0.03494947198544052</v>
       </c>
       <c r="C7">
-        <v>6.7249025628726422E-2</v>
+        <v>0.06334587598505348</v>
       </c>
       <c r="D7">
-        <v>0.10355888611341291</v>
+        <v>0.0982049983068749</v>
       </c>
       <c r="E7">
-        <v>0.103497717922563</v>
+        <v>0.09991066512808405</v>
       </c>
       <c r="F7">
-        <v>0.145526499143425</v>
+        <v>0.1450670612274896</v>
       </c>
       <c r="G7">
-        <v>0.12713694174259141</v>
+        <v>0.128320591025011</v>
       </c>
       <c r="H7">
-        <v>0.18701610019954151</v>
+        <v>0.1947355593121449</v>
       </c>
       <c r="I7">
-        <v>0.19323763732537219</v>
+        <v>0.1996990748217131</v>
       </c>
       <c r="J7">
-        <v>0.21588494235574399</v>
+        <v>0.218563672059268</v>
       </c>
       <c r="K7">
-        <v>0.23770148292430179</v>
+        <v>0.2485948799852327</v>
       </c>
       <c r="L7">
-        <v>0.3037113600701396</v>
+        <v>0.3119268710034893</v>
       </c>
       <c r="M7">
-        <v>0.35863768014061959</v>
+        <v>0.3657694351030273</v>
       </c>
       <c r="N7">
-        <v>0.35186126418251712</v>
+        <v>0.3550335194514577</v>
       </c>
       <c r="O7">
-        <v>0.34771168161774868</v>
+        <v>0.351064514404855</v>
       </c>
       <c r="P7">
-        <v>0.36390558810820328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.3706834983932646</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>3.5524059078991137E-2</v>
+        <v>0.03332693955262139</v>
       </c>
       <c r="C8">
-        <v>6.803459723925237E-2</v>
+        <v>0.06517941200178362</v>
       </c>
       <c r="D8">
-        <v>0.13445030491774981</v>
+        <v>0.1346767163176289</v>
       </c>
       <c r="E8">
-        <v>0.1629375847669696</v>
+        <v>0.1647425982946215</v>
       </c>
       <c r="F8">
-        <v>0.13532653340802339</v>
+        <v>0.1338456428874729</v>
       </c>
       <c r="G8">
-        <v>0.21698671414201279</v>
+        <v>0.2165980553036916</v>
       </c>
       <c r="H8">
-        <v>0.22679834637590751</v>
+        <v>0.2230597286404731</v>
       </c>
       <c r="I8">
-        <v>0.24206080871048069</v>
+        <v>0.240927282572229</v>
       </c>
       <c r="J8">
-        <v>0.2945553556010358</v>
+        <v>0.2995595111505513</v>
       </c>
       <c r="K8">
-        <v>0.33790323718873261</v>
+        <v>0.3420025363989241</v>
       </c>
       <c r="L8">
-        <v>0.38555470995231528</v>
+        <v>0.3840797985123268</v>
       </c>
       <c r="M8">
-        <v>0.39103341705826677</v>
+        <v>0.3877537827466838</v>
       </c>
       <c r="N8">
-        <v>0.40149735004819859</v>
+        <v>0.4013595842589971</v>
       </c>
       <c r="O8">
-        <v>0.41555223809956149</v>
+        <v>0.4167495031433662</v>
       </c>
       <c r="P8">
-        <v>0.45013139444835321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4539641597467839</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.4073602510341472E-2</v>
+        <v>0.03550000935805098</v>
       </c>
       <c r="C9">
-        <v>6.5786122915333978E-2</v>
+        <v>0.06887367155441676</v>
       </c>
       <c r="D9">
-        <v>0.13322690870709661</v>
+        <v>0.1360243913034331</v>
       </c>
       <c r="E9">
-        <v>0.16034071835707919</v>
+        <v>0.162916316180668</v>
       </c>
       <c r="F9">
-        <v>0.1299268930867811</v>
+        <v>0.1348751472163067</v>
       </c>
       <c r="G9">
-        <v>0.20322929272342941</v>
+        <v>0.2107580139292087</v>
       </c>
       <c r="H9">
-        <v>0.20768099136217241</v>
+        <v>0.2152279751201592</v>
       </c>
       <c r="I9">
-        <v>0.20915673020470149</v>
+        <v>0.2168358711552933</v>
       </c>
       <c r="J9">
-        <v>0.25547096050393142</v>
+        <v>0.2586257140808617</v>
       </c>
       <c r="K9">
-        <v>0.29575425890485663</v>
+        <v>0.2990703965371232</v>
       </c>
       <c r="L9">
-        <v>0.33655109173912462</v>
+        <v>0.3361744559125315</v>
       </c>
       <c r="M9">
-        <v>0.34467017165934921</v>
+        <v>0.3462314632564936</v>
       </c>
       <c r="N9">
-        <v>0.34217993352075349</v>
+        <v>0.3439154084414698</v>
       </c>
       <c r="O9">
-        <v>0.32642058299072341</v>
+        <v>0.3251397319807886</v>
       </c>
       <c r="P9">
-        <v>0.39178758124574209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3903677653920042</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>3.5162799041289272E-2</v>
+        <v>0.03472933464354444</v>
       </c>
       <c r="C10">
-        <v>6.6335711224038085E-2</v>
+        <v>0.06815119087410992</v>
       </c>
       <c r="D10">
-        <v>0.13356951934360509</v>
+        <v>0.1336774145594964</v>
       </c>
       <c r="E10">
-        <v>0.1617959108138354</v>
+        <v>0.1602170788303822</v>
       </c>
       <c r="F10">
-        <v>0.13446517180863829</v>
+        <v>0.1296788069198739</v>
       </c>
       <c r="G10">
-        <v>0.21183188059715449</v>
+        <v>0.2074136678552657</v>
       </c>
       <c r="H10">
-        <v>0.21488051118161319</v>
+        <v>0.2104958536758346</v>
       </c>
       <c r="I10">
-        <v>0.21547467809706361</v>
+        <v>0.2118498366675178</v>
       </c>
       <c r="J10">
-        <v>0.25685683469032478</v>
+        <v>0.253788826311144</v>
       </c>
       <c r="K10">
-        <v>0.30138629896547198</v>
+        <v>0.2958241462046439</v>
       </c>
       <c r="L10">
-        <v>0.34092320000922532</v>
+        <v>0.3304626659960047</v>
       </c>
       <c r="M10">
-        <v>0.34632337521532008</v>
+        <v>0.3367189394222718</v>
       </c>
       <c r="N10">
-        <v>0.33201928503019063</v>
+        <v>0.3303786419920673</v>
       </c>
       <c r="O10">
-        <v>0.30845676517790888</v>
+        <v>0.3094781104865547</v>
       </c>
       <c r="P10">
-        <v>0.36443891037646048</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3626133942065799</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.5530137148268193E-2</v>
+        <v>0.03651428920487643</v>
       </c>
       <c r="C11">
-        <v>6.9526356997718863E-2</v>
+        <v>0.06683413595393345</v>
       </c>
       <c r="D11">
-        <v>0.1358008561981319</v>
+        <v>0.1286582075006664</v>
       </c>
       <c r="E11">
-        <v>0.1630083589453121</v>
+        <v>0.1550241874726077</v>
       </c>
       <c r="F11">
-        <v>0.13600766060719899</v>
+        <v>0.1353161095659004</v>
       </c>
       <c r="G11">
-        <v>0.20961955250043629</v>
+        <v>0.2044387657321778</v>
       </c>
       <c r="H11">
-        <v>0.2155189485742493</v>
+        <v>0.2103593087760529</v>
       </c>
       <c r="I11">
-        <v>0.21667310596454081</v>
+        <v>0.2181935913667438</v>
       </c>
       <c r="J11">
-        <v>0.25855604658150377</v>
+        <v>0.2581916539696927</v>
       </c>
       <c r="K11">
-        <v>0.29704665833798699</v>
+        <v>0.3036987327713067</v>
       </c>
       <c r="L11">
-        <v>0.32580171017818949</v>
+        <v>0.3393674637300793</v>
       </c>
       <c r="M11">
-        <v>0.32959706734041688</v>
+        <v>0.3471091072528623</v>
       </c>
       <c r="N11">
-        <v>0.33178184457474658</v>
+        <v>0.3540372921623864</v>
       </c>
       <c r="O11">
-        <v>0.32611740414921958</v>
+        <v>0.3486506163378038</v>
       </c>
       <c r="P11">
-        <v>0.3471786064501457</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3611715819061427</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>3.2378692333682728E-2</v>
+        <v>0.03663410546311385</v>
       </c>
       <c r="C12">
-        <v>6.9183298924962555E-2</v>
+        <v>0.07390807598486254</v>
       </c>
       <c r="D12">
-        <v>0.1025001701950136</v>
+        <v>0.1064031778461719</v>
       </c>
       <c r="E12">
-        <v>0.20110669282322979</v>
+        <v>0.2051312658657264</v>
       </c>
       <c r="F12">
-        <v>0.23331735887116131</v>
+        <v>0.242675360907867</v>
       </c>
       <c r="G12">
-        <v>0.28541451444770749</v>
+        <v>0.3007129027426209</v>
       </c>
       <c r="H12">
-        <v>0.30614130642473247</v>
+        <v>0.317820189374027</v>
       </c>
       <c r="I12">
-        <v>0.30219430869504038</v>
+        <v>0.311902979147605</v>
       </c>
       <c r="J12">
-        <v>0.32295893697303329</v>
+        <v>0.3297001132336553</v>
       </c>
       <c r="K12">
-        <v>0.33292593136712051</v>
+        <v>0.3382974056382152</v>
       </c>
       <c r="L12">
-        <v>0.3982019920289025</v>
+        <v>0.4018996885101705</v>
       </c>
       <c r="M12">
-        <v>0.41052007829577758</v>
+        <v>0.4204440860497785</v>
       </c>
       <c r="N12">
-        <v>0.4598461745724155</v>
+        <v>0.4685864613942382</v>
       </c>
       <c r="O12">
-        <v>0.47443121035637031</v>
+        <v>0.4832349514248604</v>
       </c>
       <c r="P12">
-        <v>0.49889179087459312</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.506774420440212</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>3.821481064095017E-2</v>
+        <v>0.03569288224247935</v>
       </c>
       <c r="C13">
-        <v>8.6767025462380853E-2</v>
+        <v>0.08758891438826893</v>
       </c>
       <c r="D13">
-        <v>0.1233892520731828</v>
+        <v>0.1253319962058668</v>
       </c>
       <c r="E13">
-        <v>0.15693696169876881</v>
+        <v>0.1568662770090781</v>
       </c>
       <c r="F13">
-        <v>0.24947996143872411</v>
+        <v>0.2499880220727873</v>
       </c>
       <c r="G13">
-        <v>0.32174841617844002</v>
+        <v>0.3258331496503211</v>
       </c>
       <c r="H13">
-        <v>0.33881564179995349</v>
+        <v>0.3444159603444889</v>
       </c>
       <c r="I13">
-        <v>0.36196024476306049</v>
+        <v>0.3663521406128477</v>
       </c>
       <c r="J13">
-        <v>0.3843430958690135</v>
+        <v>0.3943273007793786</v>
       </c>
       <c r="K13">
-        <v>0.40117254376650868</v>
+        <v>0.4126828386504429</v>
       </c>
       <c r="L13">
-        <v>0.40896846336717912</v>
+        <v>0.4202952516865227</v>
       </c>
       <c r="M13">
-        <v>0.43029706995233979</v>
+        <v>0.4431594737893703</v>
       </c>
       <c r="N13">
-        <v>0.45577319244953551</v>
+        <v>0.4685315614216193</v>
       </c>
       <c r="O13">
-        <v>0.47987755881486632</v>
+        <v>0.492176159964384</v>
       </c>
       <c r="P13">
-        <v>0.51572006369828127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.52382568457978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>3.6361357963581392E-2</v>
+        <v>0.03633226394122999</v>
       </c>
       <c r="C14">
-        <v>6.5312125638459673E-2</v>
+        <v>0.06467022735443517</v>
       </c>
       <c r="D14">
-        <v>0.1005342126671975</v>
+        <v>0.09911644218201932</v>
       </c>
       <c r="E14">
-        <v>0.10145793540323129</v>
+        <v>0.1021994790694156</v>
       </c>
       <c r="F14">
-        <v>0.1439169621810297</v>
+        <v>0.1450361306184356</v>
       </c>
       <c r="G14">
-        <v>0.1299613364534884</v>
+        <v>0.1271507163123405</v>
       </c>
       <c r="H14">
-        <v>0.1811916580880398</v>
+        <v>0.1783088311990832</v>
       </c>
       <c r="I14">
-        <v>0.18463851675343559</v>
+        <v>0.1843603491405275</v>
       </c>
       <c r="J14">
-        <v>0.20128782314980539</v>
+        <v>0.201716436928521</v>
       </c>
       <c r="K14">
-        <v>0.2215537147319229</v>
+        <v>0.217155609992655</v>
       </c>
       <c r="L14">
-        <v>0.28051839555664548</v>
+        <v>0.2755596843107745</v>
       </c>
       <c r="M14">
-        <v>0.34602963411977222</v>
+        <v>0.3422733576408931</v>
       </c>
       <c r="N14">
-        <v>0.33441103670898398</v>
+        <v>0.3317773804845874</v>
       </c>
       <c r="O14">
-        <v>0.31734771297854258</v>
+        <v>0.3124278545686529</v>
       </c>
       <c r="P14">
-        <v>0.29967369311295111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.2914441614390099</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>3.7532612507216651E-2</v>
+        <v>0.04145192558007155</v>
       </c>
       <c r="C15">
-        <v>6.7757070817598741E-2</v>
+        <v>0.06935204379777343</v>
       </c>
       <c r="D15">
-        <v>0.1028373997799001</v>
+        <v>0.1074968692533412</v>
       </c>
       <c r="E15">
-        <v>0.10421145650406111</v>
+        <v>0.1075850155391197</v>
       </c>
       <c r="F15">
-        <v>0.14939156333212419</v>
+        <v>0.1523605529920028</v>
       </c>
       <c r="G15">
-        <v>0.133259859574827</v>
+        <v>0.136011674773608</v>
       </c>
       <c r="H15">
-        <v>0.18850688358364351</v>
+        <v>0.1939291093279129</v>
       </c>
       <c r="I15">
-        <v>0.19313741001915299</v>
+        <v>0.1938038536950704</v>
       </c>
       <c r="J15">
-        <v>0.20626370417357651</v>
+        <v>0.2089931644598788</v>
       </c>
       <c r="K15">
-        <v>0.22609724844283871</v>
+        <v>0.2278966762358693</v>
       </c>
       <c r="L15">
-        <v>0.27576977288150289</v>
+        <v>0.2813945740812371</v>
       </c>
       <c r="M15">
-        <v>0.34245335330856619</v>
+        <v>0.3497908166290569</v>
       </c>
       <c r="N15">
-        <v>0.33145554382753628</v>
+        <v>0.3338863057312477</v>
       </c>
       <c r="O15">
-        <v>0.31799724978693578</v>
+        <v>0.3221449682247713</v>
       </c>
       <c r="P15">
-        <v>0.29737023547455421</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3008967017109139</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.5556550962481892E-2</v>
+        <v>0.03828139334274661</v>
       </c>
       <c r="C16">
-        <v>6.4904169377723642E-2</v>
+        <v>0.06849762309798235</v>
       </c>
       <c r="D16">
-        <v>9.7176612149832364E-2</v>
+        <v>0.1018387258140362</v>
       </c>
       <c r="E16">
-        <v>0.10150451351781541</v>
+        <v>0.1018662155577002</v>
       </c>
       <c r="F16">
-        <v>0.14430227950203681</v>
+        <v>0.145633833986471</v>
       </c>
       <c r="G16">
-        <v>0.12738363115700169</v>
+        <v>0.1289798716697252</v>
       </c>
       <c r="H16">
-        <v>0.1808639145265776</v>
+        <v>0.181889705061818</v>
       </c>
       <c r="I16">
-        <v>0.18723173094832141</v>
+        <v>0.1871297174497941</v>
       </c>
       <c r="J16">
-        <v>0.20496828153179181</v>
+        <v>0.2049286338304296</v>
       </c>
       <c r="K16">
-        <v>0.22370745185446581</v>
+        <v>0.2225487999840288</v>
       </c>
       <c r="L16">
-        <v>0.27202001601290321</v>
+        <v>0.272228703908032</v>
       </c>
       <c r="M16">
-        <v>0.32934786288047357</v>
+        <v>0.3402954606530937</v>
       </c>
       <c r="N16">
-        <v>0.32058046319824079</v>
+        <v>0.3272277697090352</v>
       </c>
       <c r="O16">
-        <v>0.30861722041745432</v>
+        <v>0.3095139492229709</v>
       </c>
       <c r="P16">
-        <v>0.2880077572560118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2943182991739025</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>3.545098558770704E-2</v>
+        <v>0.03642383677225788</v>
       </c>
       <c r="C17">
-        <v>6.5675406095615174E-2</v>
+        <v>0.06626352897389054</v>
       </c>
       <c r="D17">
-        <v>0.10153621403907841</v>
+        <v>0.1018826434771909</v>
       </c>
       <c r="E17">
-        <v>0.1058538727857687</v>
+        <v>0.1031038498958524</v>
       </c>
       <c r="F17">
-        <v>0.14977732925039089</v>
+        <v>0.1472931186701442</v>
       </c>
       <c r="G17">
-        <v>0.12742357643063601</v>
+        <v>0.1327906782308294</v>
       </c>
       <c r="H17">
-        <v>0.18396680919334471</v>
+        <v>0.1859965197039137</v>
       </c>
       <c r="I17">
-        <v>0.1861215254406455</v>
+        <v>0.1900972582972897</v>
       </c>
       <c r="J17">
-        <v>0.20220085692756401</v>
+        <v>0.2069084628969444</v>
       </c>
       <c r="K17">
-        <v>0.2212202059793659</v>
+        <v>0.2239285245058122</v>
       </c>
       <c r="L17">
-        <v>0.27563051674935102</v>
+        <v>0.2800304626846236</v>
       </c>
       <c r="M17">
-        <v>0.33584234696874549</v>
+        <v>0.3406603142576543</v>
       </c>
       <c r="N17">
-        <v>0.3227470135390475</v>
+        <v>0.3305869953937507</v>
       </c>
       <c r="O17">
-        <v>0.30711529266637011</v>
+        <v>0.3123268901487562</v>
       </c>
       <c r="P17">
-        <v>0.28720992034353732</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.2949925244936588</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>3.3606748326183322E-2</v>
+        <v>0.03279251123910937</v>
       </c>
       <c r="C18">
-        <v>6.898800595190413E-2</v>
+        <v>0.0722352479467569</v>
       </c>
       <c r="D18">
-        <v>0.10378119412271609</v>
+        <v>0.108822312019985</v>
       </c>
       <c r="E18">
-        <v>0.1842381090910146</v>
+        <v>0.1927761950842257</v>
       </c>
       <c r="F18">
-        <v>0.22467435216040929</v>
+        <v>0.233793351839719</v>
       </c>
       <c r="G18">
-        <v>0.33960019484767467</v>
+        <v>0.3424345511143697</v>
       </c>
       <c r="H18">
-        <v>0.32600513354721672</v>
+        <v>0.3390191046698578</v>
       </c>
       <c r="I18">
-        <v>0.29931723030805751</v>
+        <v>0.3093519598272179</v>
       </c>
       <c r="J18">
-        <v>0.29691874550925179</v>
+        <v>0.3046075279165279</v>
       </c>
       <c r="K18">
-        <v>0.30011817233111771</v>
+        <v>0.3069312088943999</v>
       </c>
       <c r="L18">
-        <v>0.33905288181948379</v>
+        <v>0.3461104718263818</v>
       </c>
       <c r="M18">
-        <v>0.35475254285496982</v>
+        <v>0.3641552185239445</v>
       </c>
       <c r="N18">
-        <v>0.39102507807948811</v>
+        <v>0.4026812069270018</v>
       </c>
       <c r="O18">
-        <v>0.4051887400880102</v>
+        <v>0.4196955049691161</v>
       </c>
       <c r="P18">
-        <v>0.43213888985795701</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4409723276407398</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>3.4661297957391153E-2</v>
+        <v>0.03363498217673727</v>
       </c>
       <c r="C19">
-        <v>7.1197260429556097E-2</v>
+        <v>0.06967154420868971</v>
       </c>
       <c r="D19">
-        <v>9.7653810940902142E-2</v>
+        <v>0.09479568067974359</v>
       </c>
       <c r="E19">
-        <v>0.25342734578548409</v>
+        <v>0.2541652237702316</v>
       </c>
       <c r="F19">
-        <v>0.27675041510900172</v>
+        <v>0.2855120845344644</v>
       </c>
       <c r="G19">
-        <v>0.28565851350862992</v>
+        <v>0.2913236293060869</v>
       </c>
       <c r="H19">
-        <v>0.26668429977455399</v>
+        <v>0.2729832218492323</v>
       </c>
       <c r="I19">
-        <v>0.29308570205748358</v>
+        <v>0.2976018831769504</v>
       </c>
       <c r="J19">
-        <v>0.26630393521817092</v>
+        <v>0.2711005465740799</v>
       </c>
       <c r="K19">
-        <v>0.27726600333178802</v>
+        <v>0.282350512726918</v>
       </c>
       <c r="L19">
-        <v>0.3185496409540145</v>
+        <v>0.323161400547842</v>
       </c>
       <c r="M19">
-        <v>0.34990679967115429</v>
+        <v>0.3538051332943912</v>
       </c>
       <c r="N19">
-        <v>0.36848776385261978</v>
+        <v>0.3657667219443438</v>
       </c>
       <c r="O19">
-        <v>0.38545762951878132</v>
+        <v>0.3839467440574996</v>
       </c>
       <c r="P19">
-        <v>0.39200315179664241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3843070348226918</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>3.2003995892487258E-2</v>
+        <v>0.03394529895621773</v>
       </c>
       <c r="C20">
-        <v>5.9052934874051999E-2</v>
+        <v>0.06049111880185931</v>
       </c>
       <c r="D20">
-        <v>0.1156056804450097</v>
+        <v>0.1172745564340159</v>
       </c>
       <c r="E20">
-        <v>0.1743217053735974</v>
+        <v>0.1786106868607544</v>
       </c>
       <c r="F20">
-        <v>0.25971594663978231</v>
+        <v>0.2725401100726654</v>
       </c>
       <c r="G20">
-        <v>0.2917866371496099</v>
+        <v>0.3043785386661953</v>
       </c>
       <c r="H20">
-        <v>0.26740899203862578</v>
+        <v>0.2792517559395536</v>
       </c>
       <c r="I20">
-        <v>0.23269438527624961</v>
+        <v>0.2461775286169106</v>
       </c>
       <c r="J20">
-        <v>0.2247665237954953</v>
+        <v>0.241257638812866</v>
       </c>
       <c r="K20">
-        <v>0.26370892478780611</v>
+        <v>0.2789359225505448</v>
       </c>
       <c r="L20">
-        <v>0.29422143681426288</v>
+        <v>0.3156059954397668</v>
       </c>
       <c r="M20">
-        <v>0.32825221071921318</v>
+        <v>0.3492898563707201</v>
       </c>
       <c r="N20">
-        <v>0.3551434101704613</v>
+        <v>0.3704682913703668</v>
       </c>
       <c r="O20">
-        <v>0.35409104942828262</v>
+        <v>0.3604411997104093</v>
       </c>
       <c r="P20">
-        <v>0.36541954251320352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3716841419332581</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>4.8600569287671917E-2</v>
+        <v>0.04806424251072278</v>
       </c>
       <c r="C21">
-        <v>5.2189275385403022E-2</v>
+        <v>0.052298199630048</v>
       </c>
       <c r="D21">
-        <v>8.7732862978111115E-2</v>
+        <v>0.08492500497249594</v>
       </c>
       <c r="E21">
-        <v>0.14709781080377571</v>
+        <v>0.1452403741033849</v>
       </c>
       <c r="F21">
-        <v>0.2140918073203634</v>
+        <v>0.2060730215739127</v>
       </c>
       <c r="G21">
-        <v>0.25924401704705602</v>
+        <v>0.2482737629400648</v>
       </c>
       <c r="H21">
-        <v>0.33476355788119361</v>
+        <v>0.320995384212921</v>
       </c>
       <c r="I21">
-        <v>0.37446218828397082</v>
+        <v>0.3548063757974779</v>
       </c>
       <c r="J21">
-        <v>0.3916870703716942</v>
+        <v>0.3756478958281901</v>
       </c>
       <c r="K21">
-        <v>0.43295731933044262</v>
+        <v>0.4211997866882305</v>
       </c>
       <c r="L21">
-        <v>0.50765898045397484</v>
+        <v>0.4945315441965141</v>
       </c>
       <c r="M21">
-        <v>0.54482600363029521</v>
+        <v>0.5362581810923754</v>
       </c>
       <c r="N21">
-        <v>0.6225377640183366</v>
+        <v>0.6165727766976357</v>
       </c>
       <c r="O21">
-        <v>0.67213581980976522</v>
+        <v>0.6717494602010436</v>
       </c>
       <c r="P21">
-        <v>0.6961065338239818</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.6987313707149727</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>4.7371729209686742E-2</v>
+        <v>0.04752507296553171</v>
       </c>
       <c r="C22">
-        <v>5.1709972414544003E-2</v>
+        <v>0.05080534216977395</v>
       </c>
       <c r="D22">
-        <v>8.1936543016023433E-2</v>
+        <v>0.08282315824764053</v>
       </c>
       <c r="E22">
-        <v>0.14357344936506181</v>
+        <v>0.1437402386907364</v>
       </c>
       <c r="F22">
-        <v>0.19767184785672279</v>
+        <v>0.204483402044909</v>
       </c>
       <c r="G22">
-        <v>0.24203673465620401</v>
+        <v>0.2456096343571886</v>
       </c>
       <c r="H22">
-        <v>0.31994118118688769</v>
+        <v>0.327657095955584</v>
       </c>
       <c r="I22">
-        <v>0.37366459228048021</v>
+        <v>0.3785621785837041</v>
       </c>
       <c r="J22">
-        <v>0.39039137556997489</v>
+        <v>0.3904225706395936</v>
       </c>
       <c r="K22">
-        <v>0.43319632024510341</v>
+        <v>0.4390620953171855</v>
       </c>
       <c r="L22">
-        <v>0.50786512296075981</v>
+        <v>0.5063071718222401</v>
       </c>
       <c r="M22">
-        <v>0.54037538738133684</v>
+        <v>0.537448762032013</v>
       </c>
       <c r="N22">
-        <v>0.60331215254878467</v>
+        <v>0.591771668392381</v>
       </c>
       <c r="O22">
-        <v>0.65992950193352162</v>
+        <v>0.6578952655148715</v>
       </c>
       <c r="P22">
-        <v>0.68354029948058104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.6837131921556026</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>3.283394166836362E-2</v>
+        <v>0.03138192015844127</v>
       </c>
       <c r="C23">
-        <v>0.21080054978640031</v>
+        <v>0.2126687109269735</v>
       </c>
       <c r="D23">
-        <v>0.18623602288934521</v>
+        <v>0.1901132528709518</v>
       </c>
       <c r="E23">
-        <v>0.17281695156150731</v>
+        <v>0.1782763017733285</v>
       </c>
       <c r="F23">
-        <v>0.21112556949767181</v>
+        <v>0.2148447466459868</v>
       </c>
       <c r="G23">
-        <v>0.25631331911840233</v>
+        <v>0.253560138245047</v>
       </c>
       <c r="H23">
-        <v>0.32071185682954101</v>
+        <v>0.3142694648744065</v>
       </c>
       <c r="I23">
-        <v>0.36557737363716392</v>
+        <v>0.363467851584494</v>
       </c>
       <c r="J23">
-        <v>0.43944211414064438</v>
+        <v>0.4359132525243869</v>
       </c>
       <c r="K23">
-        <v>0.5021338394304814</v>
+        <v>0.4999926731061782</v>
       </c>
       <c r="L23">
-        <v>0.56625369713087714</v>
+        <v>0.5640596048026267</v>
       </c>
       <c r="M23">
-        <v>0.59158343114145828</v>
+        <v>0.5919301194449897</v>
       </c>
       <c r="N23">
-        <v>0.61258897479290841</v>
+        <v>0.6083735229395666</v>
       </c>
       <c r="O23">
-        <v>0.64094668998754489</v>
+        <v>0.6332074651162356</v>
       </c>
       <c r="P23">
-        <v>0.68309905305479401</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.6727670586402384</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>6.0337875897393228E-2</v>
+        <v>0.06289521785362022</v>
       </c>
       <c r="C24">
-        <v>0.2312966984450158</v>
+        <v>0.2379011829013767</v>
       </c>
       <c r="D24">
-        <v>0.28849275043328071</v>
+        <v>0.2956657611583051</v>
       </c>
       <c r="E24">
-        <v>0.41764616119384501</v>
+        <v>0.4133706581058307</v>
       </c>
       <c r="F24">
-        <v>0.64790741061891877</v>
+        <v>0.6506509241562022</v>
       </c>
       <c r="G24">
-        <v>0.76202328224094895</v>
+        <v>0.7547990773342321</v>
       </c>
       <c r="H24">
-        <v>0.80224184428261469</v>
+        <v>0.7889491536066117</v>
       </c>
       <c r="I24">
-        <v>0.91756194571280913</v>
+        <v>0.9098330934369765</v>
       </c>
       <c r="J24">
-        <v>1.0454189444123341</v>
+        <v>1.030509703865252</v>
       </c>
       <c r="K24">
-        <v>1.2741014333472109</v>
+        <v>1.256985878388695</v>
       </c>
       <c r="L24">
-        <v>1.3184754966443479</v>
+        <v>1.299156553956746</v>
       </c>
       <c r="M24">
-        <v>1.3192677969185991</v>
+        <v>1.318091573168328</v>
       </c>
       <c r="N24">
-        <v>1.3239519198889009</v>
+        <v>1.315236541086858</v>
       </c>
       <c r="O24">
-        <v>1.3194833859880071</v>
+        <v>1.309732273383011</v>
       </c>
       <c r="P24">
-        <v>1.330333646345816</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>1.315749883428398</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>8.8432705343258755E-2</v>
+        <v>0.08724906740655707</v>
       </c>
       <c r="C25">
-        <v>0.2560396212076001</v>
+        <v>0.2541979481309528</v>
       </c>
       <c r="D25">
-        <v>0.34907082055170569</v>
+        <v>0.3450546104664242</v>
       </c>
       <c r="E25">
-        <v>0.61159658734327715</v>
+        <v>0.608926740362342</v>
       </c>
       <c r="F25">
-        <v>0.66569073409170354</v>
+        <v>0.6652618441026665</v>
       </c>
       <c r="G25">
-        <v>0.83897559737860994</v>
+        <v>0.8424395128884734</v>
       </c>
       <c r="H25">
-        <v>1.14077593205302</v>
+        <v>1.153318257536764</v>
       </c>
       <c r="I25">
-        <v>1.3034476595008719</v>
+        <v>1.315264859176275</v>
       </c>
       <c r="J25">
-        <v>1.294176803238914</v>
+        <v>1.306758200749085</v>
       </c>
       <c r="K25">
-        <v>1.4029119520905109</v>
+        <v>1.417699950530074</v>
       </c>
       <c r="L25">
-        <v>1.4913900316628841</v>
+        <v>1.51714424342337</v>
       </c>
       <c r="M25">
-        <v>1.6119453181987891</v>
+        <v>1.643221471526672</v>
       </c>
       <c r="N25">
-        <v>1.73746666684312</v>
+        <v>1.772648389576269</v>
       </c>
       <c r="O25">
-        <v>1.7388301563219211</v>
+        <v>1.762615166215298</v>
       </c>
       <c r="P25">
-        <v>1.7581922025292569</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>1.77935608150283</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>5.7810182423774233E-2</v>
+        <v>0.05509752590923286</v>
       </c>
       <c r="C26">
-        <v>0.13500811314007879</v>
+        <v>0.1254414114037861</v>
       </c>
       <c r="D26">
-        <v>0.15271247340412011</v>
+        <v>0.1432951248366363</v>
       </c>
       <c r="E26">
-        <v>0.31765526484968398</v>
+        <v>0.3041146214508484</v>
       </c>
       <c r="F26">
-        <v>0.50797107761160021</v>
+        <v>0.4913321457251981</v>
       </c>
       <c r="G26">
-        <v>0.48576973919696143</v>
+        <v>0.4762178897232378</v>
       </c>
       <c r="H26">
-        <v>0.47376855075836222</v>
+        <v>0.4661355637224026</v>
       </c>
       <c r="I26">
-        <v>0.58067703452656105</v>
+        <v>0.5553475852226502</v>
       </c>
       <c r="J26">
-        <v>0.59612910023080956</v>
+        <v>0.5857887835963875</v>
       </c>
       <c r="K26">
-        <v>0.58634386526528437</v>
+        <v>0.5626274329852914</v>
       </c>
       <c r="L26">
-        <v>0.79122455851911488</v>
+        <v>0.7680483835591256</v>
       </c>
       <c r="M26">
-        <v>0.93574271582355983</v>
+        <v>0.9073060896588256</v>
       </c>
       <c r="N26">
-        <v>0.95758472588310695</v>
+        <v>0.9332128238503017</v>
       </c>
       <c r="O26">
-        <v>1.0529093744084179</v>
+        <v>1.0343644389217</v>
       </c>
       <c r="P26">
-        <v>1.1207762767305189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>1.0865541554713</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>5.8785967775336657E-2</v>
+        <v>0.05618390284359043</v>
       </c>
       <c r="C27">
-        <v>0.1048492689174618</v>
+        <v>0.1015665365852876</v>
       </c>
       <c r="D27">
-        <v>0.48682034296243831</v>
+        <v>0.4738201159450157</v>
       </c>
       <c r="E27">
-        <v>0.43898425634037502</v>
+        <v>0.433493485635903</v>
       </c>
       <c r="F27">
-        <v>0.44036953088059527</v>
+        <v>0.436202963932766</v>
       </c>
       <c r="G27">
-        <v>0.51856426804286415</v>
+        <v>0.5120642228937478</v>
       </c>
       <c r="H27">
-        <v>0.56574738571404515</v>
+        <v>0.548567432851492</v>
       </c>
       <c r="I27">
-        <v>0.55776936773535324</v>
+        <v>0.5476949219443187</v>
       </c>
       <c r="J27">
-        <v>0.71182147837103005</v>
+        <v>0.7106210653952227</v>
       </c>
       <c r="K27">
-        <v>0.812454120286769</v>
+        <v>0.8143174526377529</v>
       </c>
       <c r="L27">
-        <v>0.8703183342801748</v>
+        <v>0.8801969126450753</v>
       </c>
       <c r="M27">
-        <v>0.96905236292782471</v>
+        <v>0.9775819205163676</v>
       </c>
       <c r="N27">
-        <v>0.99753828706329672</v>
+        <v>1.011051220007392</v>
       </c>
       <c r="O27">
-        <v>1.1201183545582629</v>
+        <v>1.13925441013226</v>
       </c>
       <c r="P27">
-        <v>1.200983607569333</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>1.230997561461853</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>2.9230504314454061E-2</v>
+        <v>0.02948741842535169</v>
       </c>
       <c r="C28">
-        <v>5.9165315153553832E-2</v>
+        <v>0.05979818450748792</v>
       </c>
       <c r="D28">
-        <v>8.9431177286748986E-2</v>
+        <v>0.08886377256466649</v>
       </c>
       <c r="E28">
-        <v>9.2379003695891748E-2</v>
+        <v>0.09137939039610737</v>
       </c>
       <c r="F28">
-        <v>0.1486126795293117</v>
+        <v>0.1427593854297732</v>
       </c>
       <c r="G28">
-        <v>0.21469764760590279</v>
+        <v>0.2063665471730096</v>
       </c>
       <c r="H28">
-        <v>0.33678709289752851</v>
+        <v>0.3264948941804515</v>
       </c>
       <c r="I28">
-        <v>0.30435499753870282</v>
+        <v>0.2974440701475582</v>
       </c>
       <c r="J28">
-        <v>0.27612145933569338</v>
+        <v>0.2681912554989241</v>
       </c>
       <c r="K28">
-        <v>0.33183673165886413</v>
+        <v>0.3316604007039727</v>
       </c>
       <c r="L28">
-        <v>0.33178141121033788</v>
+        <v>0.3307475958099208</v>
       </c>
       <c r="M28">
-        <v>0.40947662538375851</v>
+        <v>0.4131485682269039</v>
       </c>
       <c r="N28">
-        <v>0.43977643340828121</v>
+        <v>0.4444180863106645</v>
       </c>
       <c r="O28">
-        <v>0.47816690178625632</v>
+        <v>0.4830253909209213</v>
       </c>
       <c r="P28">
-        <v>0.51891770231742895</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.519283926391271</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>2.9323363590416759E-2</v>
+        <v>0.0311654323988711</v>
       </c>
       <c r="C29">
-        <v>5.8607487277532233E-2</v>
+        <v>0.06310259362292242</v>
       </c>
       <c r="D29">
-        <v>9.0423665860558888E-2</v>
+        <v>0.094690264711283</v>
       </c>
       <c r="E29">
-        <v>9.1982083271474946E-2</v>
+        <v>0.09567668725662215</v>
       </c>
       <c r="F29">
-        <v>0.18184470482200021</v>
+        <v>0.1871910755450588</v>
       </c>
       <c r="G29">
-        <v>0.19361814411566389</v>
+        <v>0.2025625578968541</v>
       </c>
       <c r="H29">
-        <v>0.22995482117948199</v>
+        <v>0.2378816465909038</v>
       </c>
       <c r="I29">
-        <v>0.24012608153444329</v>
+        <v>0.2426346913709231</v>
       </c>
       <c r="J29">
-        <v>0.22105114395854009</v>
+        <v>0.2230450367272199</v>
       </c>
       <c r="K29">
-        <v>0.26030299347294239</v>
+        <v>0.2679643160208637</v>
       </c>
       <c r="L29">
-        <v>0.27988384790004911</v>
+        <v>0.2812646089970595</v>
       </c>
       <c r="M29">
-        <v>0.30424730963088392</v>
+        <v>0.3084296984210809</v>
       </c>
       <c r="N29">
-        <v>0.35290170982757602</v>
+        <v>0.3569111964611534</v>
       </c>
       <c r="O29">
-        <v>0.39471294126991902</v>
+        <v>0.4014718347232948</v>
       </c>
       <c r="P29">
-        <v>0.42995070290586118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.4383595080731429</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>2.9376307524690889E-2</v>
+        <v>0.02901155584658771</v>
       </c>
       <c r="C30">
-        <v>6.1514356250660041E-2</v>
+        <v>0.06036607065378757</v>
       </c>
       <c r="D30">
-        <v>0.1225689143802537</v>
+        <v>0.1183838961332013</v>
       </c>
       <c r="E30">
-        <v>0.11631779185183171</v>
+        <v>0.1163351764361611</v>
       </c>
       <c r="F30">
-        <v>0.16995114349511439</v>
+        <v>0.1669728433823561</v>
       </c>
       <c r="G30">
-        <v>0.22136485795791969</v>
+        <v>0.2285092900268174</v>
       </c>
       <c r="H30">
-        <v>0.27902325952030238</v>
+        <v>0.287436748832976</v>
       </c>
       <c r="I30">
-        <v>0.2368233160894167</v>
+        <v>0.2431571479958574</v>
       </c>
       <c r="J30">
-        <v>0.2670448433656305</v>
+        <v>0.2726385597940495</v>
       </c>
       <c r="K30">
-        <v>0.33342659423947912</v>
+        <v>0.3351896205572347</v>
       </c>
       <c r="L30">
-        <v>0.33971939888291058</v>
+        <v>0.3385308372031557</v>
       </c>
       <c r="M30">
-        <v>0.36333272234970948</v>
+        <v>0.3637886809472336</v>
       </c>
       <c r="N30">
-        <v>0.3904101303404981</v>
+        <v>0.3924511647425052</v>
       </c>
       <c r="O30">
-        <v>0.43355672134042123</v>
+        <v>0.4404059191517841</v>
       </c>
       <c r="P30">
-        <v>0.49114146841455469</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.4998503412342338</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>2.8023675276499741E-2</v>
+        <v>0.02702823930949039</v>
       </c>
       <c r="C31">
-        <v>6.0070137150711737E-2</v>
+        <v>0.0587660294174403</v>
       </c>
       <c r="D31">
-        <v>0.11925712541426341</v>
+        <v>0.1195892336538138</v>
       </c>
       <c r="E31">
-        <v>0.10851079310735109</v>
+        <v>0.1036739738951005</v>
       </c>
       <c r="F31">
-        <v>0.150919580125946</v>
+        <v>0.1542117921231002</v>
       </c>
       <c r="G31">
-        <v>0.18955177128862979</v>
+        <v>0.1975588457893165</v>
       </c>
       <c r="H31">
-        <v>0.24160152243741809</v>
+        <v>0.2467224404497851</v>
       </c>
       <c r="I31">
-        <v>0.20761681459466219</v>
+        <v>0.2048056954172887</v>
       </c>
       <c r="J31">
-        <v>0.19603560012454599</v>
+        <v>0.1925604230550546</v>
       </c>
       <c r="K31">
-        <v>0.23631529664399781</v>
+        <v>0.238287875731704</v>
       </c>
       <c r="L31">
-        <v>0.2271738851631242</v>
+        <v>0.2374231535885825</v>
       </c>
       <c r="M31">
-        <v>0.2276512443972456</v>
+        <v>0.2399989566445042</v>
       </c>
       <c r="N31">
-        <v>0.25294007236659688</v>
+        <v>0.2604158530923285</v>
       </c>
       <c r="O31">
-        <v>0.29810348178964902</v>
+        <v>0.3018934859406623</v>
       </c>
       <c r="P31">
-        <v>0.28387990308460742</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2863864123746487</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>2.9401227692136659E-2</v>
+        <v>0.02983892366683188</v>
       </c>
       <c r="C32">
-        <v>5.9596879411284782E-2</v>
+        <v>0.0615823919265519</v>
       </c>
       <c r="D32">
-        <v>9.2244017339662976E-2</v>
+        <v>0.09413502646520228</v>
       </c>
       <c r="E32">
-        <v>9.3348107906098488E-2</v>
+        <v>0.09475083780923227</v>
       </c>
       <c r="F32">
-        <v>0.16761712959201769</v>
+        <v>0.1686127930681744</v>
       </c>
       <c r="G32">
-        <v>0.18081578509461679</v>
+        <v>0.1779180706224408</v>
       </c>
       <c r="H32">
-        <v>0.20849281477546311</v>
+        <v>0.2077776601982431</v>
       </c>
       <c r="I32">
-        <v>0.21432963019653711</v>
+        <v>0.2160149926360139</v>
       </c>
       <c r="J32">
-        <v>0.18863946833286821</v>
+        <v>0.1918780115211344</v>
       </c>
       <c r="K32">
-        <v>0.20310519510975089</v>
+        <v>0.2040901095404043</v>
       </c>
       <c r="L32">
-        <v>0.20669299617650111</v>
+        <v>0.2105878806581479</v>
       </c>
       <c r="M32">
-        <v>0.2064294302408132</v>
+        <v>0.2102868871463121</v>
       </c>
       <c r="N32">
-        <v>0.25599836401692028</v>
+        <v>0.257182615668999</v>
       </c>
       <c r="O32">
-        <v>0.27201295285336052</v>
+        <v>0.2767851506696313</v>
       </c>
       <c r="P32">
-        <v>0.30383907739935628</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.3079437656253815</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>3.1962580720789391E-2</v>
+        <v>0.03139438907926678</v>
       </c>
       <c r="C33">
-        <v>6.3025520303084115E-2</v>
+        <v>0.06290228065945208</v>
       </c>
       <c r="D33">
-        <v>9.2956595105350315E-2</v>
+        <v>0.0940120496291198</v>
       </c>
       <c r="E33">
-        <v>9.4962537291706839E-2</v>
+        <v>0.09408201818157397</v>
       </c>
       <c r="F33">
-        <v>0.16327416455838359</v>
+        <v>0.1671754819015125</v>
       </c>
       <c r="G33">
-        <v>0.17228049267479931</v>
+        <v>0.1751451414523632</v>
       </c>
       <c r="H33">
-        <v>0.1984424378575067</v>
+        <v>0.2028143024984497</v>
       </c>
       <c r="I33">
-        <v>0.20434647729197211</v>
+        <v>0.2087557955587556</v>
       </c>
       <c r="J33">
-        <v>0.17836310401579919</v>
+        <v>0.1889189009052438</v>
       </c>
       <c r="K33">
-        <v>0.1962277636829618</v>
+        <v>0.1965800828163218</v>
       </c>
       <c r="L33">
-        <v>0.1963856412252217</v>
-      </c>
-      <c r="M33" s="2">
-        <v>0.1967417497215016</v>
+        <v>0.1985663708425143</v>
+      </c>
+      <c r="M33">
+        <v>0.1984950765911742</v>
       </c>
       <c r="N33">
-        <v>0.23827526689251041</v>
+        <v>0.2442641817119016</v>
       </c>
       <c r="O33">
-        <v>0.25096823636357291</v>
+        <v>0.2533720529247266</v>
       </c>
       <c r="P33">
-        <v>0.2920554456571105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2953987641979923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>3.1640697265449658E-2</v>
+        <v>0.02723823430598965</v>
       </c>
       <c r="C34">
-        <v>6.202030798919822E-2</v>
+        <v>0.05794142379954564</v>
       </c>
       <c r="D34">
-        <v>9.2904978388857973E-2</v>
+        <v>0.08804204180090308</v>
       </c>
       <c r="E34">
-        <v>9.4156527225168207E-2</v>
+        <v>0.09125714626376014</v>
       </c>
       <c r="F34">
-        <v>0.1681501088251289</v>
+        <v>0.1677275336637884</v>
       </c>
       <c r="G34">
-        <v>0.18455006367689369</v>
+        <v>0.1751974738116778</v>
       </c>
       <c r="H34">
-        <v>0.20475875224255269</v>
+        <v>0.2039257588680001</v>
       </c>
       <c r="I34">
-        <v>0.21634516708313059</v>
+        <v>0.2102979296797898</v>
       </c>
       <c r="J34">
-        <v>0.18610726458987981</v>
+        <v>0.1841128287815759</v>
       </c>
       <c r="K34">
-        <v>0.1990216114122588</v>
+        <v>0.1944199440277998</v>
       </c>
       <c r="L34">
-        <v>0.2033274837184684</v>
+        <v>0.1972698592651562</v>
       </c>
       <c r="M34">
-        <v>0.20589031769673929</v>
+        <v>0.1969148561280777</v>
       </c>
       <c r="N34">
-        <v>0.24590034632924099</v>
+        <v>0.2380544023732769</v>
       </c>
       <c r="O34">
-        <v>0.25387070104092779</v>
+        <v>0.2460710856600513</v>
       </c>
       <c r="P34">
-        <v>0.30117142105674388</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2893823959800579</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>3.3707847138893583E-2</v>
+        <v>0.0330865544703654</v>
       </c>
       <c r="C35">
-        <v>6.4183767073104248E-2</v>
+        <v>0.06387853810770666</v>
       </c>
       <c r="D35">
-        <v>9.5842662268329604E-2</v>
+        <v>0.09614238111122114</v>
       </c>
       <c r="E35">
-        <v>9.607690104423211E-2</v>
+        <v>0.09620314009353714</v>
       </c>
       <c r="F35">
-        <v>0.16827396280432069</v>
+        <v>0.1716741902534487</v>
       </c>
       <c r="G35">
-        <v>0.17887485647064741</v>
+        <v>0.1855462452439035</v>
       </c>
       <c r="H35">
-        <v>0.20765520751198499</v>
+        <v>0.2127509366861263</v>
       </c>
       <c r="I35">
-        <v>0.21039287874626661</v>
+        <v>0.2157362744959837</v>
       </c>
       <c r="J35">
-        <v>0.18972080306180381</v>
+        <v>0.1985029674232934</v>
       </c>
       <c r="K35">
-        <v>0.20853186415706221</v>
+        <v>0.2053325068088202</v>
       </c>
       <c r="L35">
-        <v>0.20484501818700729</v>
+        <v>0.2058357415414512</v>
       </c>
       <c r="M35">
-        <v>0.20345808197818699</v>
+        <v>0.2050436165121808</v>
       </c>
       <c r="N35">
-        <v>0.235898358606495</v>
+        <v>0.2417474234911002</v>
       </c>
       <c r="O35">
-        <v>0.24401066780600619</v>
+        <v>0.2484521379619705</v>
       </c>
       <c r="P35">
-        <v>0.28822572900196419</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.298177960974464</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>2.9512926887309051E-2</v>
+        <v>0.02801224740455999</v>
       </c>
       <c r="C36">
-        <v>5.9773987592151079E-2</v>
+        <v>0.05796428651670255</v>
       </c>
       <c r="D36">
-        <v>8.9542980637256409E-2</v>
+        <v>0.08903524432246634</v>
       </c>
       <c r="E36">
-        <v>9.2281680542941114E-2</v>
+        <v>0.09059486291890806</v>
       </c>
       <c r="F36">
-        <v>0.1704413180955337</v>
+        <v>0.1665257737319062</v>
       </c>
       <c r="G36">
-        <v>0.18273006287219509</v>
+        <v>0.1766560157731187</v>
       </c>
       <c r="H36">
-        <v>0.2118271636465299</v>
+        <v>0.2041953428924596</v>
       </c>
       <c r="I36">
-        <v>0.2145422636010377</v>
+        <v>0.2083426122222384</v>
       </c>
       <c r="J36">
-        <v>0.19796649606141831</v>
+        <v>0.1875509291045293</v>
       </c>
       <c r="K36">
-        <v>0.21615976128577949</v>
+        <v>0.2110081271150914</v>
       </c>
       <c r="L36">
-        <v>0.22356278863380499</v>
+        <v>0.2134829625259428</v>
       </c>
       <c r="M36">
-        <v>0.2303890845491344</v>
+        <v>0.2221478278633087</v>
       </c>
       <c r="N36">
-        <v>0.28250450138738759</v>
+        <v>0.2763222453911599</v>
       </c>
       <c r="O36">
-        <v>0.29676007372118668</v>
+        <v>0.2875379105224908</v>
       </c>
       <c r="P36">
-        <v>0.34003677953693351</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.3311753769798633</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>3.3068659543010859E-2</v>
+        <v>0.03187119276478062</v>
       </c>
       <c r="C37">
-        <v>6.1925104034249223E-2</v>
+        <v>0.06585828321729548</v>
       </c>
       <c r="D37">
-        <v>9.5526500726035135E-2</v>
+        <v>0.09926286620612468</v>
       </c>
       <c r="E37">
-        <v>9.5625404758254706E-2</v>
+        <v>0.0981932772797447</v>
       </c>
       <c r="F37">
-        <v>0.17154617837122399</v>
+        <v>0.1766102698328921</v>
       </c>
       <c r="G37">
-        <v>0.18572397365295801</v>
+        <v>0.1835482507644713</v>
       </c>
       <c r="H37">
-        <v>0.21815943388974851</v>
+        <v>0.2139632013228229</v>
       </c>
       <c r="I37">
-        <v>0.2154895193756789</v>
+        <v>0.2180358466298895</v>
       </c>
       <c r="J37">
-        <v>0.1905831867522918</v>
+        <v>0.2024581128141472</v>
       </c>
       <c r="K37">
-        <v>0.21191554092527479</v>
+        <v>0.2158272468204482</v>
       </c>
       <c r="L37">
-        <v>0.21927249029915971</v>
+        <v>0.222379830910585</v>
       </c>
       <c r="M37">
-        <v>0.2243793271868276</v>
+        <v>0.226230395910187</v>
       </c>
       <c r="N37">
-        <v>0.27033591393935619</v>
+        <v>0.2707586694395847</v>
       </c>
       <c r="O37">
-        <v>0.2845355505999142</v>
+        <v>0.2846394949107472</v>
       </c>
       <c r="P37">
-        <v>0.33352108109070178</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.3347014162590067</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>3.1101523390693941E-2</v>
+        <v>0.03399377073933857</v>
       </c>
       <c r="C38">
-        <v>5.9719970623370422E-2</v>
+        <v>0.06267578961722198</v>
       </c>
       <c r="D38">
-        <v>8.8263180288258136E-2</v>
+        <v>0.09339385704762199</v>
       </c>
       <c r="E38">
-        <v>8.9828144563438572E-2</v>
+        <v>0.09397651517734745</v>
       </c>
       <c r="F38">
-        <v>0.16116642112134069</v>
+        <v>0.1650413981570912</v>
       </c>
       <c r="G38">
-        <v>0.16907809757971279</v>
+        <v>0.1745672336342255</v>
       </c>
       <c r="H38">
-        <v>0.19494758665183171</v>
+        <v>0.2050145577627478</v>
       </c>
       <c r="I38">
-        <v>0.19791535492415149</v>
+        <v>0.2072639386730422</v>
       </c>
       <c r="J38">
-        <v>0.1818218929433244</v>
+        <v>0.1777725875385736</v>
       </c>
       <c r="K38">
-        <v>0.197180504435568</v>
+        <v>0.205044923465792</v>
       </c>
       <c r="L38">
-        <v>0.20348186728544471</v>
+        <v>0.2107228019216631</v>
       </c>
       <c r="M38">
-        <v>0.20790229896450321</v>
+        <v>0.2143616729563306</v>
       </c>
       <c r="N38">
-        <v>0.24873194221802139</v>
+        <v>0.2518152208761429</v>
       </c>
       <c r="O38">
-        <v>0.26454854027817881</v>
+        <v>0.2666743369230101</v>
       </c>
       <c r="P38">
-        <v>0.31510015133805058</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.3180762597483678</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>3.0211518042960291E-2</v>
+        <v>0.02995914493010898</v>
       </c>
       <c r="C39">
-        <v>6.2081160514243998E-2</v>
+        <v>0.05893832968637397</v>
       </c>
       <c r="D39">
-        <v>9.5947435813684145E-2</v>
+        <v>0.09072597323931397</v>
       </c>
       <c r="E39">
-        <v>9.5384956922609399E-2</v>
+        <v>0.09209587057783514</v>
       </c>
       <c r="F39">
-        <v>0.1707026170141516</v>
+        <v>0.1621754189104832</v>
       </c>
       <c r="G39">
-        <v>0.18531263702843159</v>
+        <v>0.1745373412972584</v>
       </c>
       <c r="H39">
-        <v>0.21034270817115169</v>
+        <v>0.2015560219326404</v>
       </c>
       <c r="I39">
-        <v>0.2170291106817456</v>
+        <v>0.2043381034803005</v>
       </c>
       <c r="J39">
-        <v>0.19015503026675301</v>
+        <v>0.1857000751166109</v>
       </c>
       <c r="K39">
-        <v>0.20859998660633641</v>
+        <v>0.2050534800383627</v>
       </c>
       <c r="L39">
-        <v>0.20987214886585229</v>
+        <v>0.2104289528149184</v>
       </c>
       <c r="M39">
-        <v>0.2130169928100735</v>
+        <v>0.2111736553418373</v>
       </c>
       <c r="N39">
-        <v>0.25348917073750071</v>
+        <v>0.2485682108373041</v>
       </c>
       <c r="O39">
-        <v>0.26992646458206032</v>
+        <v>0.2684683719448139</v>
       </c>
       <c r="P39">
-        <v>0.31135260130144637</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.3121917511336004</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>2.9864731778831251E-2</v>
+        <v>0.03090412997719943</v>
       </c>
       <c r="C40">
-        <v>5.8807494210497142E-2</v>
+        <v>0.06111134942482105</v>
       </c>
       <c r="D40">
-        <v>8.7417285963134583E-2</v>
+        <v>0.08857947186757253</v>
       </c>
       <c r="E40">
-        <v>8.9844283315660634E-2</v>
+        <v>0.08978197164566942</v>
       </c>
       <c r="F40">
-        <v>0.16361782701321231</v>
+        <v>0.1640335868753259</v>
       </c>
       <c r="G40">
-        <v>0.17137046430665709</v>
+        <v>0.1727661121652653</v>
       </c>
       <c r="H40">
-        <v>0.19425710409085431</v>
+        <v>0.1961535673543797</v>
       </c>
       <c r="I40">
-        <v>0.20021985103032561</v>
+        <v>0.2040100014774515</v>
       </c>
       <c r="J40">
-        <v>0.18063564469948151</v>
+        <v>0.1840050050251629</v>
       </c>
       <c r="K40">
-        <v>0.19459807210773439</v>
+        <v>0.2019383777956941</v>
       </c>
       <c r="L40">
-        <v>0.19538032349945619</v>
+        <v>0.1986187466556552</v>
       </c>
       <c r="M40">
-        <v>0.1976014907638716</v>
+        <v>0.1994646429688146</v>
       </c>
       <c r="N40">
-        <v>0.22990165686547409</v>
+        <v>0.2285299872403991</v>
       </c>
       <c r="O40">
-        <v>0.23489344813749591</v>
+        <v>0.2288492227209745</v>
       </c>
       <c r="P40">
-        <v>0.29378830801640587</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.2901952807566707</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>2.9376337203390279E-2</v>
+        <v>0.03238317433035665</v>
       </c>
       <c r="C41">
-        <v>0.13220697368434139</v>
+        <v>0.1344038312174641</v>
       </c>
       <c r="D41">
-        <v>9.814801544541063E-2</v>
+        <v>0.0984196287160497</v>
       </c>
       <c r="E41">
-        <v>0.1371680212441678</v>
+        <v>0.1368861308258309</v>
       </c>
       <c r="F41">
-        <v>0.2283690702568518</v>
+        <v>0.2343258365703572</v>
       </c>
       <c r="G41">
-        <v>0.37757374660533088</v>
+        <v>0.3758054057526184</v>
       </c>
       <c r="H41">
-        <v>0.39584712749293383</v>
+        <v>0.3962471010206303</v>
       </c>
       <c r="I41">
-        <v>0.40048680588983232</v>
+        <v>0.4038913327669502</v>
       </c>
       <c r="J41">
-        <v>0.42088753509722449</v>
+        <v>0.4252143151446643</v>
       </c>
       <c r="K41">
-        <v>0.42027065296540972</v>
+        <v>0.4267203652410747</v>
       </c>
       <c r="L41">
-        <v>0.47915378517924068</v>
+        <v>0.4858414722659213</v>
       </c>
       <c r="M41">
-        <v>0.5107549670427195</v>
+        <v>0.5152287333759544</v>
       </c>
       <c r="N41">
-        <v>0.53415699673058481</v>
+        <v>0.5405386368515073</v>
       </c>
       <c r="O41">
-        <v>0.54688078794347306</v>
+        <v>0.5528768258494294</v>
       </c>
       <c r="P41">
-        <v>0.56743494846167597</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.5746402178281429</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>3.0723159364262401E-2</v>
+        <v>0.0300369427044308</v>
       </c>
       <c r="C42">
-        <v>0.11822298214479759</v>
+        <v>0.1249944240890825</v>
       </c>
       <c r="D42">
-        <v>8.3797942254358881E-2</v>
+        <v>0.08956208199236698</v>
       </c>
       <c r="E42">
-        <v>0.1286557792969088</v>
+        <v>0.1373619670221743</v>
       </c>
       <c r="F42">
-        <v>0.21629393755803511</v>
+        <v>0.2269759516269975</v>
       </c>
       <c r="G42">
-        <v>0.22510061905474671</v>
+        <v>0.236048021965348</v>
       </c>
       <c r="H42">
-        <v>0.2396701025127751</v>
+        <v>0.2498594352955205</v>
       </c>
       <c r="I42">
-        <v>0.25584361176237802</v>
+        <v>0.2588566423621302</v>
       </c>
       <c r="J42">
-        <v>0.31064943145366769</v>
+        <v>0.3137618570787928</v>
       </c>
       <c r="K42">
-        <v>0.3146657009974051</v>
+        <v>0.3174944054700539</v>
       </c>
       <c r="L42">
-        <v>0.34731033538239708</v>
+        <v>0.3434115025997639</v>
       </c>
       <c r="M42">
-        <v>0.31785188378412632</v>
+        <v>0.3137879360148881</v>
       </c>
       <c r="N42">
-        <v>0.31424095915955591</v>
+        <v>0.3084503166445269</v>
       </c>
       <c r="O42">
-        <v>0.32377363555364302</v>
+        <v>0.3120169340455966</v>
       </c>
       <c r="P42">
-        <v>0.3472417973127222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.3376320836710907</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>2.7613144357835021E-2</v>
+        <v>0.03038244978037719</v>
       </c>
       <c r="C43">
-        <v>0.12066131028370659</v>
+        <v>0.1287074765120236</v>
       </c>
       <c r="D43">
-        <v>8.5264093609339064E-2</v>
+        <v>0.08814799106977067</v>
       </c>
       <c r="E43">
-        <v>0.1371251525380868</v>
+        <v>0.141324811224853</v>
       </c>
       <c r="F43">
-        <v>0.2131716103440808</v>
+        <v>0.2163935600738122</v>
       </c>
       <c r="G43">
-        <v>0.1993407573131373</v>
+        <v>0.1998857136738815</v>
       </c>
       <c r="H43">
-        <v>0.22061231796972791</v>
+        <v>0.2199040556898692</v>
       </c>
       <c r="I43">
-        <v>0.25171640026529579</v>
+        <v>0.251846362583095</v>
       </c>
       <c r="J43">
-        <v>0.27015728771008968</v>
+        <v>0.2676691596673405</v>
       </c>
       <c r="K43">
-        <v>0.26329759739892211</v>
+        <v>0.2614383835597238</v>
       </c>
       <c r="L43">
-        <v>0.3045009082866712</v>
+        <v>0.3012801018643154</v>
       </c>
       <c r="M43">
-        <v>0.28063171431371531</v>
+        <v>0.2738412817351974</v>
       </c>
       <c r="N43">
-        <v>0.28851463458291088</v>
+        <v>0.2838270647374441</v>
       </c>
       <c r="O43">
-        <v>0.29330358118988831</v>
+        <v>0.2867152161724438</v>
       </c>
       <c r="P43">
-        <v>0.32358114255411319</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.3146604469151844</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>3.9550735454690733E-2</v>
+        <v>0.03792603806362244</v>
       </c>
       <c r="C44">
-        <v>7.2654856983253691E-2</v>
+        <v>0.07360543491483107</v>
       </c>
       <c r="D44">
-        <v>7.715038694784343E-2</v>
+        <v>0.07544923649138613</v>
       </c>
       <c r="E44">
-        <v>0.1041257731594208</v>
+        <v>0.1010240425021064</v>
       </c>
       <c r="F44">
-        <v>0.20389700450037981</v>
+        <v>0.2004603828790381</v>
       </c>
       <c r="G44">
-        <v>0.22779456075581239</v>
+        <v>0.2251718663561245</v>
       </c>
       <c r="H44">
-        <v>0.26057460986884162</v>
+        <v>0.2577481785345732</v>
       </c>
       <c r="I44">
-        <v>0.30205629257698913</v>
+        <v>0.2956793233040897</v>
       </c>
       <c r="J44">
-        <v>0.35223382207538501</v>
+        <v>0.3407748348092296</v>
       </c>
       <c r="K44">
-        <v>0.409862202131835</v>
+        <v>0.4001564232157109</v>
       </c>
       <c r="L44">
-        <v>0.42032510908035919</v>
+        <v>0.408285855006883</v>
       </c>
       <c r="M44">
-        <v>0.43512113162002758</v>
+        <v>0.4229661985985816</v>
       </c>
       <c r="N44">
-        <v>0.44474968356130712</v>
+        <v>0.4360403767662712</v>
       </c>
       <c r="O44">
-        <v>0.46999922400920191</v>
+        <v>0.4623750101553286</v>
       </c>
       <c r="P44">
-        <v>0.52675538350172024</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.5154559869275672</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>5.4022239865124222E-2</v>
+        <v>0.05170095356738896</v>
       </c>
       <c r="C45">
-        <v>9.0667781603556097E-2</v>
+        <v>0.0861134574913473</v>
       </c>
       <c r="D45">
-        <v>0.1653250615090309</v>
+        <v>0.1586761068469054</v>
       </c>
       <c r="E45">
-        <v>0.24544396967184129</v>
+        <v>0.2407582448217383</v>
       </c>
       <c r="F45">
-        <v>0.32172628999299158</v>
+        <v>0.3220268258673341</v>
       </c>
       <c r="G45">
-        <v>0.39356880261924071</v>
+        <v>0.3881758543325844</v>
       </c>
       <c r="H45">
-        <v>0.43176832153213429</v>
+        <v>0.4254400023386681</v>
       </c>
       <c r="I45">
-        <v>0.46977880366232028</v>
+        <v>0.4633907311171301</v>
       </c>
       <c r="J45">
-        <v>0.50521280270401103</v>
+        <v>0.4982467229479257</v>
       </c>
       <c r="K45">
-        <v>0.59414735820205355</v>
+        <v>0.5888462939309613</v>
       </c>
       <c r="L45">
-        <v>0.64717927962958322</v>
+        <v>0.6448964615527608</v>
       </c>
       <c r="M45">
-        <v>0.68379677560798013</v>
+        <v>0.6830201303182596</v>
       </c>
       <c r="N45">
-        <v>0.7404851645599686</v>
+        <v>0.7405649780096198</v>
       </c>
       <c r="O45">
-        <v>0.7717897931172637</v>
+        <v>0.7837357051054079</v>
       </c>
       <c r="P45">
-        <v>0.76483822726334194</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>0.7798215576025513</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>5.2256247246038223E-2</v>
+        <v>0.05478576587071798</v>
       </c>
       <c r="C46">
-        <v>6.1544594218284177E-2</v>
+        <v>0.06321591573972501</v>
       </c>
       <c r="D46">
-        <v>0.12776820089595711</v>
+        <v>0.1270895562564752</v>
       </c>
       <c r="E46">
-        <v>0.23350690954952119</v>
+        <v>0.2317329058615722</v>
       </c>
       <c r="F46">
-        <v>0.34428116460443181</v>
+        <v>0.3423226980545122</v>
       </c>
       <c r="G46">
-        <v>0.35148223010313162</v>
+        <v>0.3522052205574402</v>
       </c>
       <c r="H46">
-        <v>0.37008058847556291</v>
+        <v>0.3775111380211604</v>
       </c>
       <c r="I46">
-        <v>0.41254695435272148</v>
+        <v>0.4202719984035623</v>
       </c>
       <c r="J46">
-        <v>0.5234138544569964</v>
+        <v>0.5174183589085182</v>
       </c>
       <c r="K46">
-        <v>0.61071714623405393</v>
+        <v>0.6010797301545878</v>
       </c>
       <c r="L46">
-        <v>0.65170557527805573</v>
+        <v>0.645373594834681</v>
       </c>
       <c r="M46">
-        <v>0.72342775891259115</v>
+        <v>0.7170173361779578</v>
       </c>
       <c r="N46">
-        <v>0.77006075526983708</v>
+        <v>0.7555444649642307</v>
       </c>
       <c r="O46">
-        <v>0.76703370787978187</v>
+        <v>0.7516725591983349</v>
       </c>
       <c r="P46">
-        <v>0.769574287601412</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.7492535268976899</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>3.8242420924828269E-2</v>
+        <v>0.03742389974724009</v>
       </c>
       <c r="C47">
-        <v>0.1032069706215681</v>
+        <v>0.1042725238419298</v>
       </c>
       <c r="D47">
-        <v>0.16397910323676709</v>
+        <v>0.1657644515122551</v>
       </c>
       <c r="E47">
-        <v>0.23219768632483109</v>
+        <v>0.2338965409278375</v>
       </c>
       <c r="F47">
-        <v>0.3183846126395668</v>
+        <v>0.3153828679280637</v>
       </c>
       <c r="G47">
-        <v>0.34797393022262929</v>
+        <v>0.3454134199146452</v>
       </c>
       <c r="H47">
-        <v>0.36656401003891892</v>
+        <v>0.3623406984941953</v>
       </c>
       <c r="I47">
-        <v>0.40195142200182299</v>
+        <v>0.3997393041587702</v>
       </c>
       <c r="J47">
-        <v>0.50627209643344817</v>
+        <v>0.5067535526610714</v>
       </c>
       <c r="K47">
-        <v>0.52397203987343699</v>
+        <v>0.5311676797920096</v>
       </c>
       <c r="L47">
-        <v>0.55311319178493767</v>
+        <v>0.5635557067642939</v>
       </c>
       <c r="M47">
-        <v>0.59573284746591126</v>
+        <v>0.6043872298568578</v>
       </c>
       <c r="N47">
-        <v>0.60323185997267093</v>
+        <v>0.6070247920961522</v>
       </c>
       <c r="O47">
-        <v>0.62365576269904632</v>
+        <v>0.6331493975221478</v>
       </c>
       <c r="P47">
-        <v>0.6489507112608045</v>
+        <v>0.6545146878567367</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P32 B34:P47 B33:L33 N33:P33">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_diff.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -443,49 +443,49 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.03973040546005044</v>
+        <v>0.03687667563150734</v>
       </c>
       <c r="C2">
-        <v>0.07427153771119521</v>
+        <v>0.06985115036465561</v>
       </c>
       <c r="D2">
-        <v>0.100041008761757</v>
+        <v>0.09649927877929076</v>
       </c>
       <c r="E2">
-        <v>0.1039197714386337</v>
+        <v>0.1026024456752657</v>
       </c>
       <c r="F2">
-        <v>0.1651278530609113</v>
+        <v>0.1579321252366</v>
       </c>
       <c r="G2">
-        <v>0.1536940718332843</v>
+        <v>0.1459886399117452</v>
       </c>
       <c r="H2">
-        <v>0.1661361754323425</v>
+        <v>0.1585196392321675</v>
       </c>
       <c r="I2">
-        <v>0.1934143912996075</v>
+        <v>0.1892564999866198</v>
       </c>
       <c r="J2">
-        <v>0.2368061540648556</v>
+        <v>0.227085428697574</v>
       </c>
       <c r="K2">
-        <v>0.2796041920247191</v>
+        <v>0.2698023529870114</v>
       </c>
       <c r="L2">
-        <v>0.2876726830364041</v>
+        <v>0.276106223332684</v>
       </c>
       <c r="M2">
-        <v>0.3427161571962502</v>
+        <v>0.3326061205531013</v>
       </c>
       <c r="N2">
-        <v>0.3546652476508932</v>
+        <v>0.3413098892625038</v>
       </c>
       <c r="O2">
-        <v>0.3962602282775642</v>
+        <v>0.3800428991572884</v>
       </c>
       <c r="P2">
-        <v>0.3909918852779004</v>
+        <v>0.3797922807955131</v>
       </c>
     </row>
     <row r="3">
@@ -495,49 +495,49 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.04853158050493867</v>
+        <v>0.05327591057487951</v>
       </c>
       <c r="C3">
-        <v>0.05160142424280179</v>
+        <v>0.05634336380711313</v>
       </c>
       <c r="D3">
-        <v>0.09180381838711554</v>
+        <v>0.09543423559566699</v>
       </c>
       <c r="E3">
-        <v>0.1712583482043571</v>
+        <v>0.1628235753486844</v>
       </c>
       <c r="F3">
-        <v>0.2382326855596571</v>
+        <v>0.2357862209976676</v>
       </c>
       <c r="G3">
-        <v>0.2684542074698905</v>
+        <v>0.2678864744107483</v>
       </c>
       <c r="H3">
-        <v>0.3358472676706087</v>
+        <v>0.3392092569985795</v>
       </c>
       <c r="I3">
-        <v>0.3895004874767821</v>
+        <v>0.3958660096565333</v>
       </c>
       <c r="J3">
-        <v>0.4157323499797297</v>
+        <v>0.421366076810861</v>
       </c>
       <c r="K3">
-        <v>0.4383140940677869</v>
+        <v>0.4399204921572253</v>
       </c>
       <c r="L3">
-        <v>0.4880769389738813</v>
+        <v>0.4945871195593192</v>
       </c>
       <c r="M3">
-        <v>0.5394951992493471</v>
+        <v>0.5431865612952734</v>
       </c>
       <c r="N3">
-        <v>0.5958687162210324</v>
+        <v>0.6010086573199911</v>
       </c>
       <c r="O3">
-        <v>0.6576958380425331</v>
+        <v>0.6685227635547659</v>
       </c>
       <c r="P3">
-        <v>0.6887702065823996</v>
+        <v>0.7026919909768998</v>
       </c>
     </row>
     <row r="4">
@@ -547,49 +547,49 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.03724389129458505</v>
+        <v>0.0348121601524341</v>
       </c>
       <c r="C4">
-        <v>0.07048287513836277</v>
+        <v>0.06584093520610523</v>
       </c>
       <c r="D4">
-        <v>0.08543346611944502</v>
+        <v>0.08197255507236711</v>
       </c>
       <c r="E4">
-        <v>0.1580177749866928</v>
+        <v>0.1553553866861721</v>
       </c>
       <c r="F4">
-        <v>0.1611940115434754</v>
+        <v>0.1532475555140382</v>
       </c>
       <c r="G4">
-        <v>0.2127976745742741</v>
+        <v>0.200368742187342</v>
       </c>
       <c r="H4">
-        <v>0.2212091919747212</v>
+        <v>0.2112950672702095</v>
       </c>
       <c r="I4">
-        <v>0.2618690928448231</v>
+        <v>0.2492648498800921</v>
       </c>
       <c r="J4">
-        <v>0.2890936104800714</v>
+        <v>0.2773467294278777</v>
       </c>
       <c r="K4">
-        <v>0.3804798141171343</v>
+        <v>0.3680848009919085</v>
       </c>
       <c r="L4">
-        <v>0.4212979275102951</v>
+        <v>0.4135230584341951</v>
       </c>
       <c r="M4">
-        <v>0.4464081092852262</v>
+        <v>0.4357926781672743</v>
       </c>
       <c r="N4">
-        <v>0.4478712395956488</v>
+        <v>0.4382910378375866</v>
       </c>
       <c r="O4">
-        <v>0.4727445387646012</v>
+        <v>0.4562605144416328</v>
       </c>
       <c r="P4">
-        <v>0.5237543281662649</v>
+        <v>0.502607774682577</v>
       </c>
     </row>
     <row r="5">
@@ -599,49 +599,49 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.03523251527970223</v>
+        <v>0.03677688999262918</v>
       </c>
       <c r="C5">
-        <v>0.0709691252211867</v>
+        <v>0.07546507848533285</v>
       </c>
       <c r="D5">
-        <v>0.09916776184024839</v>
+        <v>0.1042072093610814</v>
       </c>
       <c r="E5">
-        <v>0.1729847444118246</v>
+        <v>0.1806859688876513</v>
       </c>
       <c r="F5">
-        <v>0.2315595629742016</v>
+        <v>0.2348856057673362</v>
       </c>
       <c r="G5">
-        <v>0.3230525487928471</v>
+        <v>0.3150989324650215</v>
       </c>
       <c r="H5">
-        <v>0.3476053804466632</v>
+        <v>0.3408523700236281</v>
       </c>
       <c r="I5">
-        <v>0.3576970253169757</v>
+        <v>0.3528005845892719</v>
       </c>
       <c r="J5">
-        <v>0.3686228007975192</v>
+        <v>0.3641288282361706</v>
       </c>
       <c r="K5">
-        <v>0.4066644016296214</v>
+        <v>0.4055657322193214</v>
       </c>
       <c r="L5">
-        <v>0.4371293223339679</v>
+        <v>0.4314854277201129</v>
       </c>
       <c r="M5">
-        <v>0.4780055811310777</v>
+        <v>0.4688653956129137</v>
       </c>
       <c r="N5">
-        <v>0.5391385539487288</v>
+        <v>0.5242901831599385</v>
       </c>
       <c r="O5">
-        <v>0.5440760336142536</v>
+        <v>0.531477471604419</v>
       </c>
       <c r="P5">
-        <v>0.5874833217325173</v>
+        <v>0.572960293624045</v>
       </c>
     </row>
     <row r="6">
@@ -651,49 +651,49 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.03172043734825086</v>
+        <v>0.03380771793442916</v>
       </c>
       <c r="C6">
-        <v>0.06507633673295782</v>
+        <v>0.06868695293239402</v>
       </c>
       <c r="D6">
-        <v>0.08921137398311496</v>
+        <v>0.09250654828806087</v>
       </c>
       <c r="E6">
-        <v>0.2399878810979922</v>
+        <v>0.2431056928807256</v>
       </c>
       <c r="F6">
-        <v>0.2390958090638362</v>
+        <v>0.2393708571939283</v>
       </c>
       <c r="G6">
-        <v>0.313877546547211</v>
+        <v>0.302122726379597</v>
       </c>
       <c r="H6">
-        <v>0.3263084479419723</v>
+        <v>0.321585752057314</v>
       </c>
       <c r="I6">
-        <v>0.3182127611213387</v>
+        <v>0.313564978429786</v>
       </c>
       <c r="J6">
-        <v>0.3572308196138028</v>
+        <v>0.349223392804074</v>
       </c>
       <c r="K6">
-        <v>0.3857784313392849</v>
+        <v>0.3795652189386254</v>
       </c>
       <c r="L6">
-        <v>0.4300664865544335</v>
+        <v>0.4300764408191522</v>
       </c>
       <c r="M6">
-        <v>0.489066306021916</v>
+        <v>0.4858552344725734</v>
       </c>
       <c r="N6">
-        <v>0.5346327155572879</v>
+        <v>0.5294523099777333</v>
       </c>
       <c r="O6">
-        <v>0.5523320264005198</v>
+        <v>0.5495626931026436</v>
       </c>
       <c r="P6">
-        <v>0.5395488832184715</v>
+        <v>0.5364334194743861</v>
       </c>
     </row>
     <row r="7">
@@ -703,49 +703,49 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.03494947198544052</v>
+        <v>0.03565460529775605</v>
       </c>
       <c r="C7">
-        <v>0.06334587598505348</v>
+        <v>0.0658294807957987</v>
       </c>
       <c r="D7">
-        <v>0.0982049983068749</v>
+        <v>0.1007786996546259</v>
       </c>
       <c r="E7">
-        <v>0.09991066512808405</v>
+        <v>0.1033389532487885</v>
       </c>
       <c r="F7">
-        <v>0.1450670612274896</v>
+        <v>0.1528768798690602</v>
       </c>
       <c r="G7">
-        <v>0.128320591025011</v>
+        <v>0.1287223193149564</v>
       </c>
       <c r="H7">
-        <v>0.1947355593121449</v>
+        <v>0.2006257801429795</v>
       </c>
       <c r="I7">
-        <v>0.1996990748217131</v>
+        <v>0.2053939798111573</v>
       </c>
       <c r="J7">
-        <v>0.218563672059268</v>
+        <v>0.224404939603129</v>
       </c>
       <c r="K7">
-        <v>0.2485948799852327</v>
+        <v>0.2490663564087146</v>
       </c>
       <c r="L7">
-        <v>0.3119268710034893</v>
+        <v>0.3113499515763503</v>
       </c>
       <c r="M7">
-        <v>0.3657694351030273</v>
+        <v>0.3656447854991924</v>
       </c>
       <c r="N7">
-        <v>0.3550335194514577</v>
+        <v>0.3538326911042169</v>
       </c>
       <c r="O7">
-        <v>0.351064514404855</v>
+        <v>0.3489571211277753</v>
       </c>
       <c r="P7">
-        <v>0.3706834983932646</v>
+        <v>0.3666931118081058</v>
       </c>
     </row>
     <row r="8">
@@ -755,49 +755,49 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03332693955262139</v>
+        <v>0.03136140443565621</v>
       </c>
       <c r="C8">
-        <v>0.06517941200178362</v>
+        <v>0.06481845042986867</v>
       </c>
       <c r="D8">
-        <v>0.1346767163176289</v>
+        <v>0.131209616244237</v>
       </c>
       <c r="E8">
-        <v>0.1647425982946215</v>
+        <v>0.1598111807743281</v>
       </c>
       <c r="F8">
-        <v>0.1338456428874729</v>
+        <v>0.1332507037191292</v>
       </c>
       <c r="G8">
-        <v>0.2165980553036916</v>
+        <v>0.2146059805719043</v>
       </c>
       <c r="H8">
-        <v>0.2230597286404731</v>
+        <v>0.2232834253017029</v>
       </c>
       <c r="I8">
-        <v>0.240927282572229</v>
+        <v>0.2366738965958372</v>
       </c>
       <c r="J8">
-        <v>0.2995595111505513</v>
+        <v>0.2963027714240693</v>
       </c>
       <c r="K8">
-        <v>0.3420025363989241</v>
+        <v>0.3411077274683285</v>
       </c>
       <c r="L8">
-        <v>0.3840797985123268</v>
+        <v>0.3813897856094922</v>
       </c>
       <c r="M8">
-        <v>0.3877537827466838</v>
+        <v>0.387931960077824</v>
       </c>
       <c r="N8">
-        <v>0.4013595842589971</v>
+        <v>0.3941871674355892</v>
       </c>
       <c r="O8">
-        <v>0.4167495031433662</v>
+        <v>0.4091022020435546</v>
       </c>
       <c r="P8">
-        <v>0.4539641597467839</v>
+        <v>0.4466531580639098</v>
       </c>
     </row>
     <row r="9">
@@ -807,49 +807,49 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.03550000935805098</v>
+        <v>0.03441686348208456</v>
       </c>
       <c r="C9">
-        <v>0.06887367155441676</v>
+        <v>0.06515645260742936</v>
       </c>
       <c r="D9">
-        <v>0.1360243913034331</v>
+        <v>0.1288041171922328</v>
       </c>
       <c r="E9">
-        <v>0.162916316180668</v>
+        <v>0.1561757158888233</v>
       </c>
       <c r="F9">
-        <v>0.1348751472163067</v>
+        <v>0.1252877438093284</v>
       </c>
       <c r="G9">
-        <v>0.2107580139292087</v>
+        <v>0.1994850161468578</v>
       </c>
       <c r="H9">
-        <v>0.2152279751201592</v>
+        <v>0.2027222121461203</v>
       </c>
       <c r="I9">
-        <v>0.2168358711552933</v>
+        <v>0.2084369572548073</v>
       </c>
       <c r="J9">
-        <v>0.2586257140808617</v>
+        <v>0.2485014377462253</v>
       </c>
       <c r="K9">
-        <v>0.2990703965371232</v>
+        <v>0.2873376260318984</v>
       </c>
       <c r="L9">
-        <v>0.3361744559125315</v>
+        <v>0.3288181034577493</v>
       </c>
       <c r="M9">
-        <v>0.3462314632564936</v>
+        <v>0.3339496712884498</v>
       </c>
       <c r="N9">
-        <v>0.3439154084414698</v>
+        <v>0.3293775566829511</v>
       </c>
       <c r="O9">
-        <v>0.3251397319807886</v>
+        <v>0.310372584500104</v>
       </c>
       <c r="P9">
-        <v>0.3903677653920042</v>
+        <v>0.3717799484218025</v>
       </c>
     </row>
     <row r="10">
@@ -859,49 +859,49 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.03472933464354444</v>
+        <v>0.03332709290231717</v>
       </c>
       <c r="C10">
-        <v>0.06815119087410992</v>
+        <v>0.06478640576881717</v>
       </c>
       <c r="D10">
-        <v>0.1336774145594964</v>
+        <v>0.1261338212130899</v>
       </c>
       <c r="E10">
-        <v>0.1602170788303822</v>
+        <v>0.1526406039982728</v>
       </c>
       <c r="F10">
-        <v>0.1296788069198739</v>
+        <v>0.1299357316251518</v>
       </c>
       <c r="G10">
-        <v>0.2074136678552657</v>
+        <v>0.1983925021255235</v>
       </c>
       <c r="H10">
-        <v>0.2104958536758346</v>
+        <v>0.2068405515885031</v>
       </c>
       <c r="I10">
-        <v>0.2118498366675178</v>
+        <v>0.2103061980461622</v>
       </c>
       <c r="J10">
-        <v>0.253788826311144</v>
+        <v>0.2520522953559001</v>
       </c>
       <c r="K10">
-        <v>0.2958241462046439</v>
+        <v>0.2881027624998208</v>
       </c>
       <c r="L10">
-        <v>0.3304626659960047</v>
+        <v>0.326457106172614</v>
       </c>
       <c r="M10">
-        <v>0.3367189394222718</v>
+        <v>0.33086286206837</v>
       </c>
       <c r="N10">
-        <v>0.3303786419920673</v>
+        <v>0.3230694899416701</v>
       </c>
       <c r="O10">
-        <v>0.3094781104865547</v>
+        <v>0.3043299366145015</v>
       </c>
       <c r="P10">
-        <v>0.3626133942065799</v>
+        <v>0.3636228184830802</v>
       </c>
     </row>
     <row r="11">
@@ -911,49 +911,49 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.03651428920487643</v>
+        <v>0.03583585717983973</v>
       </c>
       <c r="C11">
-        <v>0.06683413595393345</v>
+        <v>0.06818756781363577</v>
       </c>
       <c r="D11">
-        <v>0.1286582075006664</v>
+        <v>0.1370768364365663</v>
       </c>
       <c r="E11">
-        <v>0.1550241874726077</v>
+        <v>0.1672199467249438</v>
       </c>
       <c r="F11">
-        <v>0.1353161095659004</v>
+        <v>0.1456071087849261</v>
       </c>
       <c r="G11">
-        <v>0.2044387657321778</v>
+        <v>0.2193283084086243</v>
       </c>
       <c r="H11">
-        <v>0.2103593087760529</v>
+        <v>0.225555933670608</v>
       </c>
       <c r="I11">
-        <v>0.2181935913667438</v>
+        <v>0.226894702530837</v>
       </c>
       <c r="J11">
-        <v>0.2581916539696927</v>
+        <v>0.2662925174320634</v>
       </c>
       <c r="K11">
-        <v>0.3036987327713067</v>
+        <v>0.3118224049428477</v>
       </c>
       <c r="L11">
-        <v>0.3393674637300793</v>
+        <v>0.346672999777001</v>
       </c>
       <c r="M11">
-        <v>0.3471091072528623</v>
+        <v>0.3497142847031727</v>
       </c>
       <c r="N11">
-        <v>0.3540372921623864</v>
+        <v>0.3543795908209443</v>
       </c>
       <c r="O11">
-        <v>0.3486506163378038</v>
+        <v>0.3465818561797681</v>
       </c>
       <c r="P11">
-        <v>0.3611715819061427</v>
+        <v>0.3627267685383074</v>
       </c>
     </row>
     <row r="12">
@@ -963,49 +963,49 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.03663410546311385</v>
+        <v>0.0343376468941759</v>
       </c>
       <c r="C12">
-        <v>0.07390807598486254</v>
+        <v>0.06920031792436948</v>
       </c>
       <c r="D12">
-        <v>0.1064031778461719</v>
+        <v>0.1003518290074051</v>
       </c>
       <c r="E12">
-        <v>0.2051312658657264</v>
+        <v>0.195047145347099</v>
       </c>
       <c r="F12">
-        <v>0.242675360907867</v>
+        <v>0.2336585805962811</v>
       </c>
       <c r="G12">
-        <v>0.3007129027426209</v>
+        <v>0.2917748110550128</v>
       </c>
       <c r="H12">
-        <v>0.317820189374027</v>
+        <v>0.3089726352460643</v>
       </c>
       <c r="I12">
-        <v>0.311902979147605</v>
+        <v>0.2994425588572177</v>
       </c>
       <c r="J12">
-        <v>0.3297001132336553</v>
+        <v>0.3199379448133314</v>
       </c>
       <c r="K12">
-        <v>0.3382974056382152</v>
+        <v>0.3277981262471645</v>
       </c>
       <c r="L12">
-        <v>0.4018996885101705</v>
+        <v>0.3932247776913809</v>
       </c>
       <c r="M12">
-        <v>0.4204440860497785</v>
+        <v>0.4113252886962289</v>
       </c>
       <c r="N12">
-        <v>0.4685864613942382</v>
+        <v>0.4581395049123144</v>
       </c>
       <c r="O12">
-        <v>0.4832349514248604</v>
+        <v>0.4763271290194497</v>
       </c>
       <c r="P12">
-        <v>0.506774420440212</v>
+        <v>0.5027216113553756</v>
       </c>
     </row>
     <row r="13">
@@ -1015,49 +1015,49 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.03569288224247935</v>
+        <v>0.03585384700198724</v>
       </c>
       <c r="C13">
-        <v>0.08758891438826893</v>
+        <v>0.08695501610838779</v>
       </c>
       <c r="D13">
-        <v>0.1253319962058668</v>
+        <v>0.1264713831622781</v>
       </c>
       <c r="E13">
-        <v>0.1568662770090781</v>
+        <v>0.1604598468227473</v>
       </c>
       <c r="F13">
-        <v>0.2499880220727873</v>
+        <v>0.2533913925262508</v>
       </c>
       <c r="G13">
-        <v>0.3258331496503211</v>
+        <v>0.3270729957162917</v>
       </c>
       <c r="H13">
-        <v>0.3444159603444889</v>
+        <v>0.3485514316771466</v>
       </c>
       <c r="I13">
-        <v>0.3663521406128477</v>
+        <v>0.3740308471685311</v>
       </c>
       <c r="J13">
-        <v>0.3943273007793786</v>
+        <v>0.3995004259400214</v>
       </c>
       <c r="K13">
-        <v>0.4126828386504429</v>
+        <v>0.4188871281143282</v>
       </c>
       <c r="L13">
-        <v>0.4202952516865227</v>
+        <v>0.4270482085231414</v>
       </c>
       <c r="M13">
-        <v>0.4431594737893703</v>
+        <v>0.4505428831576491</v>
       </c>
       <c r="N13">
-        <v>0.4685315614216193</v>
+        <v>0.4779678400514874</v>
       </c>
       <c r="O13">
-        <v>0.492176159964384</v>
+        <v>0.5031015862559901</v>
       </c>
       <c r="P13">
-        <v>0.52382568457978</v>
+        <v>0.5390648626229024</v>
       </c>
     </row>
     <row r="14">
@@ -1067,49 +1067,49 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.03633226394122999</v>
+        <v>0.03491042270111155</v>
       </c>
       <c r="C14">
-        <v>0.06467022735443517</v>
+        <v>0.06436721852689975</v>
       </c>
       <c r="D14">
-        <v>0.09911644218201932</v>
+        <v>0.10117884048568</v>
       </c>
       <c r="E14">
-        <v>0.1021994790694156</v>
+        <v>0.1004203295203078</v>
       </c>
       <c r="F14">
-        <v>0.1450361306184356</v>
+        <v>0.143750473834863</v>
       </c>
       <c r="G14">
-        <v>0.1271507163123405</v>
+        <v>0.1305637933648512</v>
       </c>
       <c r="H14">
-        <v>0.1783088311990832</v>
+        <v>0.1802161962702689</v>
       </c>
       <c r="I14">
-        <v>0.1843603491405275</v>
+        <v>0.187226852400065</v>
       </c>
       <c r="J14">
-        <v>0.201716436928521</v>
+        <v>0.2028566784512133</v>
       </c>
       <c r="K14">
-        <v>0.217155609992655</v>
+        <v>0.2235017512706474</v>
       </c>
       <c r="L14">
-        <v>0.2755596843107745</v>
+        <v>0.2791799121126301</v>
       </c>
       <c r="M14">
-        <v>0.3422733576408931</v>
+        <v>0.3459060410641922</v>
       </c>
       <c r="N14">
-        <v>0.3317773804845874</v>
+        <v>0.3354731083893424</v>
       </c>
       <c r="O14">
-        <v>0.3124278545686529</v>
+        <v>0.3214001393396493</v>
       </c>
       <c r="P14">
-        <v>0.2914441614390099</v>
+        <v>0.3042707271148185</v>
       </c>
     </row>
     <row r="15">
@@ -1119,49 +1119,49 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.04145192558007155</v>
+        <v>0.03531278351268224</v>
       </c>
       <c r="C15">
-        <v>0.06935204379777343</v>
+        <v>0.06184232843970788</v>
       </c>
       <c r="D15">
-        <v>0.1074968692533412</v>
+        <v>0.09249304085752846</v>
       </c>
       <c r="E15">
-        <v>0.1075850155391197</v>
+        <v>0.09665986553003209</v>
       </c>
       <c r="F15">
-        <v>0.1523605529920028</v>
+        <v>0.139514379253021</v>
       </c>
       <c r="G15">
-        <v>0.136011674773608</v>
+        <v>0.1205255495708184</v>
       </c>
       <c r="H15">
-        <v>0.1939291093279129</v>
+        <v>0.1757050886759799</v>
       </c>
       <c r="I15">
-        <v>0.1938038536950704</v>
+        <v>0.1822083655564698</v>
       </c>
       <c r="J15">
-        <v>0.2089931644598788</v>
+        <v>0.1980728896218625</v>
       </c>
       <c r="K15">
-        <v>0.2278966762358693</v>
+        <v>0.215625033203328</v>
       </c>
       <c r="L15">
-        <v>0.2813945740812371</v>
+        <v>0.2686101736980437</v>
       </c>
       <c r="M15">
-        <v>0.3497908166290569</v>
+        <v>0.3327226643406129</v>
       </c>
       <c r="N15">
-        <v>0.3338863057312477</v>
+        <v>0.3151157787025938</v>
       </c>
       <c r="O15">
-        <v>0.3221449682247713</v>
+        <v>0.2976927233746006</v>
       </c>
       <c r="P15">
-        <v>0.3008967017109139</v>
+        <v>0.2840428279546475</v>
       </c>
     </row>
     <row r="16">
@@ -1171,49 +1171,49 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.03828139334274661</v>
+        <v>0.0367740245520361</v>
       </c>
       <c r="C16">
-        <v>0.06849762309798235</v>
+        <v>0.06811784559083883</v>
       </c>
       <c r="D16">
-        <v>0.1018387258140362</v>
+        <v>0.1061378403959337</v>
       </c>
       <c r="E16">
-        <v>0.1018662155577002</v>
+        <v>0.1065309502533015</v>
       </c>
       <c r="F16">
-        <v>0.145633833986471</v>
+        <v>0.1558912840749933</v>
       </c>
       <c r="G16">
-        <v>0.1289798716697252</v>
+        <v>0.1341158718077475</v>
       </c>
       <c r="H16">
-        <v>0.181889705061818</v>
+        <v>0.1882762621365923</v>
       </c>
       <c r="I16">
-        <v>0.1871297174497941</v>
+        <v>0.1908042996173197</v>
       </c>
       <c r="J16">
-        <v>0.2049286338304296</v>
+        <v>0.2054109547167501</v>
       </c>
       <c r="K16">
-        <v>0.2225487999840288</v>
+        <v>0.2224251137130338</v>
       </c>
       <c r="L16">
-        <v>0.272228703908032</v>
+        <v>0.2672364931797097</v>
       </c>
       <c r="M16">
-        <v>0.3402954606530937</v>
+        <v>0.3226501020369424</v>
       </c>
       <c r="N16">
-        <v>0.3272277697090352</v>
+        <v>0.3083029847684718</v>
       </c>
       <c r="O16">
-        <v>0.3095139492229709</v>
+        <v>0.2955541535316042</v>
       </c>
       <c r="P16">
-        <v>0.2943182991739025</v>
+        <v>0.2765557158375289</v>
       </c>
     </row>
     <row r="17">
@@ -1223,49 +1223,49 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.03642383677225788</v>
+        <v>0.03617155472083583</v>
       </c>
       <c r="C17">
-        <v>0.06626352897389054</v>
+        <v>0.06733937872749807</v>
       </c>
       <c r="D17">
-        <v>0.1018826434771909</v>
+        <v>0.1008675758286723</v>
       </c>
       <c r="E17">
-        <v>0.1031038498958524</v>
+        <v>0.1022962751297558</v>
       </c>
       <c r="F17">
-        <v>0.1472931186701442</v>
+        <v>0.1455154241163457</v>
       </c>
       <c r="G17">
-        <v>0.1327906782308294</v>
+        <v>0.1291438930765433</v>
       </c>
       <c r="H17">
-        <v>0.1859965197039137</v>
+        <v>0.1835648072125364</v>
       </c>
       <c r="I17">
-        <v>0.1900972582972897</v>
+        <v>0.1845356299742839</v>
       </c>
       <c r="J17">
-        <v>0.2069084628969444</v>
+        <v>0.1993125016185448</v>
       </c>
       <c r="K17">
-        <v>0.2239285245058122</v>
+        <v>0.2146120122693422</v>
       </c>
       <c r="L17">
-        <v>0.2800304626846236</v>
+        <v>0.267700154397993</v>
       </c>
       <c r="M17">
-        <v>0.3406603142576543</v>
+        <v>0.3257260321409571</v>
       </c>
       <c r="N17">
-        <v>0.3305869953937507</v>
+        <v>0.3143278710881512</v>
       </c>
       <c r="O17">
-        <v>0.3123268901487562</v>
+        <v>0.2956404696430175</v>
       </c>
       <c r="P17">
-        <v>0.2949925244936588</v>
+        <v>0.2819228571369267</v>
       </c>
     </row>
     <row r="18">
@@ -1275,49 +1275,49 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.03279251123910937</v>
+        <v>0.03316286132117391</v>
       </c>
       <c r="C18">
-        <v>0.0722352479467569</v>
+        <v>0.06913000526392171</v>
       </c>
       <c r="D18">
-        <v>0.108822312019985</v>
+        <v>0.1042877427535815</v>
       </c>
       <c r="E18">
-        <v>0.1927761950842257</v>
+        <v>0.1868243813144833</v>
       </c>
       <c r="F18">
-        <v>0.233793351839719</v>
+        <v>0.2336619882457868</v>
       </c>
       <c r="G18">
-        <v>0.3424345511143697</v>
+        <v>0.3402164925253222</v>
       </c>
       <c r="H18">
-        <v>0.3390191046698578</v>
+        <v>0.3347564440796182</v>
       </c>
       <c r="I18">
-        <v>0.3093519598272179</v>
+        <v>0.3026896270669482</v>
       </c>
       <c r="J18">
-        <v>0.3046075279165279</v>
+        <v>0.2962577757694462</v>
       </c>
       <c r="K18">
-        <v>0.3069312088943999</v>
+        <v>0.300103150593149</v>
       </c>
       <c r="L18">
-        <v>0.3461104718263818</v>
+        <v>0.3340215993864613</v>
       </c>
       <c r="M18">
-        <v>0.3641552185239445</v>
+        <v>0.3541076729216663</v>
       </c>
       <c r="N18">
-        <v>0.4026812069270018</v>
+        <v>0.3922546483367891</v>
       </c>
       <c r="O18">
-        <v>0.4196955049691161</v>
+        <v>0.4098627553473861</v>
       </c>
       <c r="P18">
-        <v>0.4409723276407398</v>
+        <v>0.4344981447953572</v>
       </c>
     </row>
     <row r="19">
@@ -1327,49 +1327,49 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.03363498217673727</v>
+        <v>0.03346615759984128</v>
       </c>
       <c r="C19">
-        <v>0.06967154420868971</v>
+        <v>0.07012069742900101</v>
       </c>
       <c r="D19">
-        <v>0.09479568067974359</v>
+        <v>0.09572553890900581</v>
       </c>
       <c r="E19">
-        <v>0.2541652237702316</v>
+        <v>0.2498523885895509</v>
       </c>
       <c r="F19">
-        <v>0.2855120845344644</v>
+        <v>0.284677769387166</v>
       </c>
       <c r="G19">
-        <v>0.2913236293060869</v>
+        <v>0.2863844842515355</v>
       </c>
       <c r="H19">
-        <v>0.2729832218492323</v>
+        <v>0.2677978205608592</v>
       </c>
       <c r="I19">
-        <v>0.2976018831769504</v>
+        <v>0.2975594803968028</v>
       </c>
       <c r="J19">
-        <v>0.2711005465740799</v>
+        <v>0.2728184709430861</v>
       </c>
       <c r="K19">
-        <v>0.282350512726918</v>
+        <v>0.2841108704583877</v>
       </c>
       <c r="L19">
-        <v>0.323161400547842</v>
+        <v>0.326567349389591</v>
       </c>
       <c r="M19">
-        <v>0.3538051332943912</v>
+        <v>0.3603041681163637</v>
       </c>
       <c r="N19">
-        <v>0.3657667219443438</v>
+        <v>0.3732983172829401</v>
       </c>
       <c r="O19">
-        <v>0.3839467440574996</v>
+        <v>0.3862219037550862</v>
       </c>
       <c r="P19">
-        <v>0.3843070348226918</v>
+        <v>0.3918944860615575</v>
       </c>
     </row>
     <row r="20">
@@ -1379,49 +1379,49 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.03394529895621773</v>
+        <v>0.03311648718221644</v>
       </c>
       <c r="C20">
-        <v>0.06049111880185931</v>
+        <v>0.05853109034976967</v>
       </c>
       <c r="D20">
-        <v>0.1172745564340159</v>
+        <v>0.1121579071252726</v>
       </c>
       <c r="E20">
-        <v>0.1786106868607544</v>
+        <v>0.1713220293446263</v>
       </c>
       <c r="F20">
-        <v>0.2725401100726654</v>
+        <v>0.262102286872527</v>
       </c>
       <c r="G20">
-        <v>0.3043785386661953</v>
+        <v>0.2908788867037214</v>
       </c>
       <c r="H20">
-        <v>0.2792517559395536</v>
+        <v>0.274786456524262</v>
       </c>
       <c r="I20">
-        <v>0.2461775286169106</v>
+        <v>0.2375333771657042</v>
       </c>
       <c r="J20">
-        <v>0.241257638812866</v>
+        <v>0.2364040277737436</v>
       </c>
       <c r="K20">
-        <v>0.2789359225505448</v>
+        <v>0.2745911846147257</v>
       </c>
       <c r="L20">
-        <v>0.3156059954397668</v>
+        <v>0.3019691650061245</v>
       </c>
       <c r="M20">
-        <v>0.3492898563707201</v>
+        <v>0.3364973017188613</v>
       </c>
       <c r="N20">
-        <v>0.3704682913703668</v>
+        <v>0.3577514207808967</v>
       </c>
       <c r="O20">
-        <v>0.3604411997104093</v>
+        <v>0.3522839298809439</v>
       </c>
       <c r="P20">
-        <v>0.3716841419332581</v>
+        <v>0.3603469447066773</v>
       </c>
     </row>
     <row r="21">
@@ -1431,49 +1431,49 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.04806424251072278</v>
+        <v>0.052995594355426</v>
       </c>
       <c r="C21">
-        <v>0.052298199630048</v>
+        <v>0.05614326005473896</v>
       </c>
       <c r="D21">
-        <v>0.08492500497249594</v>
+        <v>0.08956582126818219</v>
       </c>
       <c r="E21">
-        <v>0.1452403741033849</v>
+        <v>0.151109470343094</v>
       </c>
       <c r="F21">
-        <v>0.2060730215739127</v>
+        <v>0.21135370526291</v>
       </c>
       <c r="G21">
-        <v>0.2482737629400648</v>
+        <v>0.2551729651436768</v>
       </c>
       <c r="H21">
-        <v>0.320995384212921</v>
+        <v>0.3203971106588837</v>
       </c>
       <c r="I21">
-        <v>0.3548063757974779</v>
+        <v>0.3536490475001617</v>
       </c>
       <c r="J21">
-        <v>0.3756478958281901</v>
+        <v>0.3764300150268171</v>
       </c>
       <c r="K21">
-        <v>0.4211997866882305</v>
+        <v>0.4154980321488995</v>
       </c>
       <c r="L21">
-        <v>0.4945315441965141</v>
+        <v>0.4875100012314311</v>
       </c>
       <c r="M21">
-        <v>0.5362581810923754</v>
+        <v>0.5208535232464422</v>
       </c>
       <c r="N21">
-        <v>0.6165727766976357</v>
+        <v>0.602842191225188</v>
       </c>
       <c r="O21">
-        <v>0.6717494602010436</v>
+        <v>0.6540618508285672</v>
       </c>
       <c r="P21">
-        <v>0.6987313707149727</v>
+        <v>0.6890271445162298</v>
       </c>
     </row>
     <row r="22">
@@ -1483,49 +1483,49 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.04752507296553171</v>
+        <v>0.04787408939751675</v>
       </c>
       <c r="C22">
-        <v>0.05080534216977395</v>
+        <v>0.05299292744449818</v>
       </c>
       <c r="D22">
-        <v>0.08282315824764053</v>
+        <v>0.08505531692610935</v>
       </c>
       <c r="E22">
-        <v>0.1437402386907364</v>
+        <v>0.1453247353211125</v>
       </c>
       <c r="F22">
-        <v>0.204483402044909</v>
+        <v>0.2062022422208261</v>
       </c>
       <c r="G22">
-        <v>0.2456096343571886</v>
+        <v>0.2444772173007216</v>
       </c>
       <c r="H22">
-        <v>0.327657095955584</v>
+        <v>0.3275706974974453</v>
       </c>
       <c r="I22">
-        <v>0.3785621785837041</v>
+        <v>0.3831674872846821</v>
       </c>
       <c r="J22">
-        <v>0.3904225706395936</v>
+        <v>0.3970499532037334</v>
       </c>
       <c r="K22">
-        <v>0.4390620953171855</v>
+        <v>0.4463335847202958</v>
       </c>
       <c r="L22">
-        <v>0.5063071718222401</v>
+        <v>0.5127727548350435</v>
       </c>
       <c r="M22">
-        <v>0.537448762032013</v>
+        <v>0.5421245859875646</v>
       </c>
       <c r="N22">
-        <v>0.591771668392381</v>
+        <v>0.6043156797759062</v>
       </c>
       <c r="O22">
-        <v>0.6578952655148715</v>
+        <v>0.6669749529635263</v>
       </c>
       <c r="P22">
-        <v>0.6837131921556026</v>
+        <v>0.6910296096146911</v>
       </c>
     </row>
     <row r="23">
@@ -1535,1297 +1535,1089 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.03138192015844127</v>
+        <v>0.03092152612624588</v>
       </c>
       <c r="C23">
-        <v>0.2126687109269735</v>
+        <v>0.2103494843831584</v>
       </c>
       <c r="D23">
-        <v>0.1901132528709518</v>
+        <v>0.1819678178249414</v>
       </c>
       <c r="E23">
-        <v>0.1782763017733285</v>
+        <v>0.164881119418215</v>
       </c>
       <c r="F23">
-        <v>0.2148447466459868</v>
+        <v>0.2067138494589167</v>
       </c>
       <c r="G23">
-        <v>0.253560138245047</v>
+        <v>0.2498294361521359</v>
       </c>
       <c r="H23">
-        <v>0.3142694648744065</v>
+        <v>0.3145515308082865</v>
       </c>
       <c r="I23">
-        <v>0.363467851584494</v>
+        <v>0.3635897466342422</v>
       </c>
       <c r="J23">
-        <v>0.4359132525243869</v>
+        <v>0.4332329116602953</v>
       </c>
       <c r="K23">
-        <v>0.4999926731061782</v>
+        <v>0.4876262498067289</v>
       </c>
       <c r="L23">
-        <v>0.5640596048026267</v>
+        <v>0.552236685163163</v>
       </c>
       <c r="M23">
-        <v>0.5919301194449897</v>
+        <v>0.5821431832733318</v>
       </c>
       <c r="N23">
-        <v>0.6083735229395666</v>
+        <v>0.6025342841164334</v>
       </c>
       <c r="O23">
-        <v>0.6332074651162356</v>
+        <v>0.6332772171234524</v>
       </c>
       <c r="P23">
-        <v>0.6727670586402384</v>
+        <v>0.6792879726844505</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.06289521785362022</v>
+        <v>0.03025099473910969</v>
       </c>
       <c r="C24">
-        <v>0.2379011829013767</v>
+        <v>0.06208755415399109</v>
       </c>
       <c r="D24">
-        <v>0.2956657611583051</v>
+        <v>0.09192041875345325</v>
       </c>
       <c r="E24">
-        <v>0.4133706581058307</v>
+        <v>0.09361633784991991</v>
       </c>
       <c r="F24">
-        <v>0.6506509241562022</v>
+        <v>0.1459631206494484</v>
       </c>
       <c r="G24">
-        <v>0.7547990773342321</v>
+        <v>0.2070361751465235</v>
       </c>
       <c r="H24">
-        <v>0.7889491536066117</v>
+        <v>0.322953997522566</v>
       </c>
       <c r="I24">
-        <v>0.9098330934369765</v>
+        <v>0.2899031393843063</v>
       </c>
       <c r="J24">
-        <v>1.030509703865252</v>
+        <v>0.2671423264152073</v>
       </c>
       <c r="K24">
-        <v>1.256985878388695</v>
+        <v>0.3317609551416162</v>
       </c>
       <c r="L24">
-        <v>1.299156553956746</v>
+        <v>0.3306132586071248</v>
       </c>
       <c r="M24">
-        <v>1.318091573168328</v>
+        <v>0.411593542302746</v>
       </c>
       <c r="N24">
-        <v>1.315236541086858</v>
+        <v>0.4427602982839624</v>
       </c>
       <c r="O24">
-        <v>1.309732273383011</v>
+        <v>0.4818673787075331</v>
       </c>
       <c r="P24">
-        <v>1.315749883428398</v>
+        <v>0.5203526440751789</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.08724906740655707</v>
+        <v>0.03020546043110001</v>
       </c>
       <c r="C25">
-        <v>0.2541979481309528</v>
+        <v>0.05981300008011758</v>
       </c>
       <c r="D25">
-        <v>0.3450546104664242</v>
+        <v>0.09188229351890331</v>
       </c>
       <c r="E25">
-        <v>0.608926740362342</v>
+        <v>0.09485895145618251</v>
       </c>
       <c r="F25">
-        <v>0.6652618441026665</v>
+        <v>0.1815913513963484</v>
       </c>
       <c r="G25">
-        <v>0.8424395128884734</v>
+        <v>0.1928943934577623</v>
       </c>
       <c r="H25">
-        <v>1.153318257536764</v>
+        <v>0.2316987472604768</v>
       </c>
       <c r="I25">
-        <v>1.315264859176275</v>
+        <v>0.2394402532060466</v>
       </c>
       <c r="J25">
-        <v>1.306758200749085</v>
+        <v>0.2188103040733695</v>
       </c>
       <c r="K25">
-        <v>1.417699950530074</v>
+        <v>0.2679611909073628</v>
       </c>
       <c r="L25">
-        <v>1.51714424342337</v>
+        <v>0.2789610758142635</v>
       </c>
       <c r="M25">
-        <v>1.643221471526672</v>
+        <v>0.3023806653809331</v>
       </c>
       <c r="N25">
-        <v>1.772648389576269</v>
+        <v>0.3529703630016533</v>
       </c>
       <c r="O25">
-        <v>1.762615166215298</v>
+        <v>0.3939093568123333</v>
       </c>
       <c r="P25">
-        <v>1.77935608150283</v>
+        <v>0.4326508809528936</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.05509752590923286</v>
+        <v>0.02773971523654767</v>
       </c>
       <c r="C26">
-        <v>0.1254414114037861</v>
+        <v>0.0601039322444929</v>
       </c>
       <c r="D26">
-        <v>0.1432951248366363</v>
+        <v>0.1178931510682164</v>
       </c>
       <c r="E26">
-        <v>0.3041146214508484</v>
+        <v>0.1147847941060101</v>
       </c>
       <c r="F26">
-        <v>0.4913321457251981</v>
+        <v>0.1678957654942453</v>
       </c>
       <c r="G26">
-        <v>0.4762178897232378</v>
+        <v>0.227415605236352</v>
       </c>
       <c r="H26">
-        <v>0.4661355637224026</v>
+        <v>0.2843492862930455</v>
       </c>
       <c r="I26">
-        <v>0.5553475852226502</v>
+        <v>0.2401038058833868</v>
       </c>
       <c r="J26">
-        <v>0.5857887835963875</v>
+        <v>0.2681921557718758</v>
       </c>
       <c r="K26">
-        <v>0.5626274329852914</v>
+        <v>0.3308861790387297</v>
       </c>
       <c r="L26">
-        <v>0.7680483835591256</v>
+        <v>0.3353408042338289</v>
       </c>
       <c r="M26">
-        <v>0.9073060896588256</v>
+        <v>0.3596011321167214</v>
       </c>
       <c r="N26">
-        <v>0.9332128238503017</v>
+        <v>0.3888533644955432</v>
       </c>
       <c r="O26">
-        <v>1.0343644389217</v>
+        <v>0.4309205282187574</v>
       </c>
       <c r="P26">
-        <v>1.0865541554713</v>
+        <v>0.4892930387849304</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.05618390284359043</v>
+        <v>0.02790836924026086</v>
       </c>
       <c r="C27">
-        <v>0.1015665365852876</v>
+        <v>0.05752958647917017</v>
       </c>
       <c r="D27">
-        <v>0.4738201159450157</v>
+        <v>0.1118158610256764</v>
       </c>
       <c r="E27">
-        <v>0.433493485635903</v>
+        <v>0.1047003108006156</v>
       </c>
       <c r="F27">
-        <v>0.436202963932766</v>
+        <v>0.1464124390602912</v>
       </c>
       <c r="G27">
-        <v>0.5120642228937478</v>
+        <v>0.1868591183582479</v>
       </c>
       <c r="H27">
-        <v>0.548567432851492</v>
+        <v>0.2365413004089432</v>
       </c>
       <c r="I27">
-        <v>0.5476949219443187</v>
+        <v>0.2050432607851377</v>
       </c>
       <c r="J27">
-        <v>0.7106210653952227</v>
+        <v>0.1950078631767435</v>
       </c>
       <c r="K27">
-        <v>0.8143174526377529</v>
+        <v>0.2375215598915554</v>
       </c>
       <c r="L27">
-        <v>0.8801969126450753</v>
+        <v>0.2343361408190562</v>
       </c>
       <c r="M27">
-        <v>0.9775819205163676</v>
+        <v>0.2327566844376211</v>
       </c>
       <c r="N27">
-        <v>1.011051220007392</v>
+        <v>0.2606888145131284</v>
       </c>
       <c r="O27">
-        <v>1.13925441013226</v>
+        <v>0.3020934811921751</v>
       </c>
       <c r="P27">
-        <v>1.230997561461853</v>
+        <v>0.2873844380685808</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.02948741842535169</v>
+        <v>0.03012484381850605</v>
       </c>
       <c r="C28">
-        <v>0.05979818450748792</v>
+        <v>0.06021623740548343</v>
       </c>
       <c r="D28">
-        <v>0.08886377256466649</v>
+        <v>0.09192879636663143</v>
       </c>
       <c r="E28">
-        <v>0.09137939039610737</v>
+        <v>0.09372810541276694</v>
       </c>
       <c r="F28">
-        <v>0.1427593854297732</v>
+        <v>0.1680961908291787</v>
       </c>
       <c r="G28">
-        <v>0.2063665471730096</v>
+        <v>0.1792569360204492</v>
       </c>
       <c r="H28">
-        <v>0.3264948941804515</v>
+        <v>0.2070271994981925</v>
       </c>
       <c r="I28">
-        <v>0.2974440701475582</v>
+        <v>0.2087250610958216</v>
       </c>
       <c r="J28">
-        <v>0.2681912554989241</v>
+        <v>0.1837368353963382</v>
       </c>
       <c r="K28">
-        <v>0.3316604007039727</v>
+        <v>0.1943939635333746</v>
       </c>
       <c r="L28">
-        <v>0.3307475958099208</v>
+        <v>0.2049037049712042</v>
       </c>
       <c r="M28">
-        <v>0.4131485682269039</v>
+        <v>0.2061480648020403</v>
       </c>
       <c r="N28">
-        <v>0.4444180863106645</v>
+        <v>0.2542530278435561</v>
       </c>
       <c r="O28">
-        <v>0.4830253909209213</v>
+        <v>0.2733579628225244</v>
       </c>
       <c r="P28">
-        <v>0.519283926391271</v>
+        <v>0.3007825424938555</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.0311654323988711</v>
+        <v>0.03254180408465851</v>
       </c>
       <c r="C29">
-        <v>0.06310259362292242</v>
+        <v>0.06529658731254212</v>
       </c>
       <c r="D29">
-        <v>0.094690264711283</v>
+        <v>0.09664230711959526</v>
       </c>
       <c r="E29">
-        <v>0.09567668725662215</v>
+        <v>0.09710897931409235</v>
       </c>
       <c r="F29">
-        <v>0.1871910755450588</v>
+        <v>0.1719334259346535</v>
       </c>
       <c r="G29">
-        <v>0.2025625578968541</v>
+        <v>0.1791909189726862</v>
       </c>
       <c r="H29">
-        <v>0.2378816465909038</v>
+        <v>0.2096534955491376</v>
       </c>
       <c r="I29">
-        <v>0.2426346913709231</v>
+        <v>0.2144475153773582</v>
       </c>
       <c r="J29">
-        <v>0.2230450367272199</v>
+        <v>0.1913093615115103</v>
       </c>
       <c r="K29">
-        <v>0.2679643160208637</v>
+        <v>0.1964799057685773</v>
       </c>
       <c r="L29">
-        <v>0.2812646089970595</v>
+        <v>0.1995042432059493</v>
       </c>
       <c r="M29">
-        <v>0.3084296984210809</v>
+        <v>0.2008717569048206</v>
       </c>
       <c r="N29">
-        <v>0.3569111964611534</v>
+        <v>0.2441961006541405</v>
       </c>
       <c r="O29">
-        <v>0.4014718347232948</v>
+        <v>0.2569048978346783</v>
       </c>
       <c r="P29">
-        <v>0.4383595080731429</v>
+        <v>0.2950329433349758</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.02901155584658771</v>
+        <v>0.02950940352726572</v>
       </c>
       <c r="C30">
-        <v>0.06036607065378757</v>
+        <v>0.05961515394166872</v>
       </c>
       <c r="D30">
-        <v>0.1183838961332013</v>
+        <v>0.09072075927577711</v>
       </c>
       <c r="E30">
-        <v>0.1163351764361611</v>
+        <v>0.09160195065389493</v>
       </c>
       <c r="F30">
-        <v>0.1669728433823561</v>
+        <v>0.1685643650790505</v>
       </c>
       <c r="G30">
-        <v>0.2285092900268174</v>
+        <v>0.1770523788317124</v>
       </c>
       <c r="H30">
-        <v>0.287436748832976</v>
+        <v>0.2020636909399154</v>
       </c>
       <c r="I30">
-        <v>0.2431571479958574</v>
+        <v>0.2109011281582753</v>
       </c>
       <c r="J30">
-        <v>0.2726385597940495</v>
+        <v>0.1837899136882881</v>
       </c>
       <c r="K30">
-        <v>0.3351896205572347</v>
+        <v>0.2012940583107707</v>
       </c>
       <c r="L30">
-        <v>0.3385308372031557</v>
+        <v>0.199421448097343</v>
       </c>
       <c r="M30">
-        <v>0.3637886809472336</v>
+        <v>0.2010880137716332</v>
       </c>
       <c r="N30">
-        <v>0.3924511647425052</v>
+        <v>0.2470001106503366</v>
       </c>
       <c r="O30">
-        <v>0.4404059191517841</v>
+        <v>0.2531285581435521</v>
       </c>
       <c r="P30">
-        <v>0.4998503412342338</v>
+        <v>0.2983992323637508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.02702823930949039</v>
+        <v>0.02925312828442062</v>
       </c>
       <c r="C31">
-        <v>0.0587660294174403</v>
+        <v>0.05908445930888989</v>
       </c>
       <c r="D31">
-        <v>0.1195892336538138</v>
+        <v>0.08755891362628831</v>
       </c>
       <c r="E31">
-        <v>0.1036739738951005</v>
+        <v>0.08924386181901001</v>
       </c>
       <c r="F31">
-        <v>0.1542117921231002</v>
+        <v>0.1588223889764758</v>
       </c>
       <c r="G31">
-        <v>0.1975588457893165</v>
+        <v>0.1719609997097362</v>
       </c>
       <c r="H31">
-        <v>0.2467224404497851</v>
+        <v>0.1987147387622608</v>
       </c>
       <c r="I31">
-        <v>0.2048056954172887</v>
+        <v>0.2079407635681428</v>
       </c>
       <c r="J31">
-        <v>0.1925604230550546</v>
+        <v>0.1807477322587376</v>
       </c>
       <c r="K31">
-        <v>0.238287875731704</v>
+        <v>0.1942042936564741</v>
       </c>
       <c r="L31">
-        <v>0.2374231535885825</v>
+        <v>0.1938794102308012</v>
       </c>
       <c r="M31">
-        <v>0.2399989566445042</v>
+        <v>0.1940205896567667</v>
       </c>
       <c r="N31">
-        <v>0.2604158530923285</v>
+        <v>0.2286566621031065</v>
       </c>
       <c r="O31">
-        <v>0.3018934859406623</v>
+        <v>0.2330857100494945</v>
       </c>
       <c r="P31">
-        <v>0.2863864123746487</v>
+        <v>0.2792121905811108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.02983892366683188</v>
+        <v>0.02989324897729528</v>
       </c>
       <c r="C32">
-        <v>0.0615823919265519</v>
+        <v>0.05956860518384816</v>
       </c>
       <c r="D32">
-        <v>0.09413502646520228</v>
+        <v>0.09015685240952964</v>
       </c>
       <c r="E32">
-        <v>0.09475083780923227</v>
+        <v>0.09184829302823738</v>
       </c>
       <c r="F32">
-        <v>0.1686127930681744</v>
+        <v>0.1697211833793738</v>
       </c>
       <c r="G32">
-        <v>0.1779180706224408</v>
+        <v>0.1805256408956634</v>
       </c>
       <c r="H32">
-        <v>0.2077776601982431</v>
+        <v>0.2162538013771075</v>
       </c>
       <c r="I32">
-        <v>0.2160149926360139</v>
+        <v>0.2128947253155541</v>
       </c>
       <c r="J32">
-        <v>0.1918780115211344</v>
+        <v>0.1955734001773241</v>
       </c>
       <c r="K32">
-        <v>0.2040901095404043</v>
+        <v>0.2135993923882084</v>
       </c>
       <c r="L32">
-        <v>0.2105878806581479</v>
+        <v>0.2223309313865023</v>
       </c>
       <c r="M32">
-        <v>0.2102868871463121</v>
+        <v>0.2267848257719908</v>
       </c>
       <c r="N32">
-        <v>0.257182615668999</v>
+        <v>0.2802764835761515</v>
       </c>
       <c r="O32">
-        <v>0.2767851506696313</v>
+        <v>0.2933245285362388</v>
       </c>
       <c r="P32">
-        <v>0.3079437656253815</v>
+        <v>0.3399699835736554</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.03139438907926678</v>
+        <v>0.03448591904607418</v>
       </c>
       <c r="C33">
-        <v>0.06290228065945208</v>
+        <v>0.06583581864439558</v>
       </c>
       <c r="D33">
-        <v>0.0940120496291198</v>
+        <v>0.09429765939792434</v>
       </c>
       <c r="E33">
-        <v>0.09408201818157397</v>
+        <v>0.09646516601198335</v>
       </c>
       <c r="F33">
-        <v>0.1671754819015125</v>
+        <v>0.1759906527741237</v>
       </c>
       <c r="G33">
-        <v>0.1751451414523632</v>
+        <v>0.1888302828090936</v>
       </c>
       <c r="H33">
-        <v>0.2028143024984497</v>
+        <v>0.2123585699156663</v>
       </c>
       <c r="I33">
-        <v>0.2087557955587556</v>
+        <v>0.2089095774934795</v>
       </c>
       <c r="J33">
-        <v>0.1889189009052438</v>
+        <v>0.1914583416446595</v>
       </c>
       <c r="K33">
-        <v>0.1965800828163218</v>
+        <v>0.2052140252208825</v>
       </c>
       <c r="L33">
-        <v>0.1985663708425143</v>
+        <v>0.2109917313716396</v>
       </c>
       <c r="M33">
-        <v>0.1984950765911742</v>
+        <v>0.2165021552440154</v>
       </c>
       <c r="N33">
-        <v>0.2442641817119016</v>
+        <v>0.2604578356066796</v>
       </c>
       <c r="O33">
-        <v>0.2533720529247266</v>
+        <v>0.2796864678439581</v>
       </c>
       <c r="P33">
-        <v>0.2953987641979923</v>
+        <v>0.3265759247184767</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.02723823430598965</v>
+        <v>0.03236965630326039</v>
       </c>
       <c r="C34">
-        <v>0.05794142379954564</v>
+        <v>0.06171281501802772</v>
       </c>
       <c r="D34">
-        <v>0.08804204180090308</v>
+        <v>0.09445448165871245</v>
       </c>
       <c r="E34">
-        <v>0.09125714626376014</v>
+        <v>0.09556590445825047</v>
       </c>
       <c r="F34">
-        <v>0.1677275336637884</v>
+        <v>0.1662997533485808</v>
       </c>
       <c r="G34">
-        <v>0.1751974738116778</v>
+        <v>0.1752207411678167</v>
       </c>
       <c r="H34">
-        <v>0.2039257588680001</v>
+        <v>0.1999213138885526</v>
       </c>
       <c r="I34">
-        <v>0.2102979296797898</v>
+        <v>0.2088803056255544</v>
       </c>
       <c r="J34">
-        <v>0.1841128287815759</v>
+        <v>0.1897013196917534</v>
       </c>
       <c r="K34">
-        <v>0.1944199440277998</v>
+        <v>0.2083185440219332</v>
       </c>
       <c r="L34">
-        <v>0.1972698592651562</v>
+        <v>0.2164609445792085</v>
       </c>
       <c r="M34">
-        <v>0.1969148561280777</v>
+        <v>0.2191107571326472</v>
       </c>
       <c r="N34">
-        <v>0.2380544023732769</v>
+        <v>0.263199297120559</v>
       </c>
       <c r="O34">
-        <v>0.2460710856600513</v>
+        <v>0.2780750085253071</v>
       </c>
       <c r="P34">
-        <v>0.2893823959800579</v>
+        <v>0.3355997410080142</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.0330865544703654</v>
+        <v>0.03160278538676792</v>
       </c>
       <c r="C35">
-        <v>0.06387853810770666</v>
+        <v>0.06205118738369875</v>
       </c>
       <c r="D35">
-        <v>0.09614238111122114</v>
+        <v>0.09247753870731978</v>
       </c>
       <c r="E35">
-        <v>0.09620314009353714</v>
+        <v>0.09286772688925038</v>
       </c>
       <c r="F35">
-        <v>0.1716741902534487</v>
+        <v>0.1624226212476406</v>
       </c>
       <c r="G35">
-        <v>0.1855462452439035</v>
+        <v>0.1708110726437139</v>
       </c>
       <c r="H35">
-        <v>0.2127509366861263</v>
+        <v>0.2011885935239617</v>
       </c>
       <c r="I35">
-        <v>0.2157362744959837</v>
+        <v>0.2072621143577572</v>
       </c>
       <c r="J35">
-        <v>0.1985029674232934</v>
+        <v>0.1828974381893402</v>
       </c>
       <c r="K35">
-        <v>0.2053325068088202</v>
+        <v>0.2087564284041451</v>
       </c>
       <c r="L35">
-        <v>0.2058357415414512</v>
+        <v>0.2067236660103537</v>
       </c>
       <c r="M35">
-        <v>0.2050436165121808</v>
+        <v>0.2092476215634375</v>
       </c>
       <c r="N35">
-        <v>0.2417474234911002</v>
+        <v>0.2438982480915948</v>
       </c>
       <c r="O35">
-        <v>0.2484521379619705</v>
+        <v>0.266082446435564</v>
       </c>
       <c r="P35">
-        <v>0.298177960974464</v>
+        <v>0.3078298379275011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.02801224740455999</v>
+        <v>0.0303763320655383</v>
       </c>
       <c r="C36">
-        <v>0.05796428651670255</v>
+        <v>0.05963615259348387</v>
       </c>
       <c r="D36">
-        <v>0.08903524432246634</v>
+        <v>0.08947582552858274</v>
       </c>
       <c r="E36">
-        <v>0.09059486291890806</v>
+        <v>0.09041044705939316</v>
       </c>
       <c r="F36">
-        <v>0.1665257737319062</v>
+        <v>0.161363979061503</v>
       </c>
       <c r="G36">
-        <v>0.1766560157731187</v>
+        <v>0.1680825354656124</v>
       </c>
       <c r="H36">
-        <v>0.2041953428924596</v>
+        <v>0.1962293440581712</v>
       </c>
       <c r="I36">
-        <v>0.2083426122222384</v>
+        <v>0.2064007399966422</v>
       </c>
       <c r="J36">
-        <v>0.1875509291045293</v>
+        <v>0.180150585198935</v>
       </c>
       <c r="K36">
-        <v>0.2110081271150914</v>
+        <v>0.193324992805801</v>
       </c>
       <c r="L36">
-        <v>0.2134829625259428</v>
+        <v>0.1941283646026088</v>
       </c>
       <c r="M36">
-        <v>0.2221478278633087</v>
+        <v>0.1968821876190096</v>
       </c>
       <c r="N36">
-        <v>0.2763222453911599</v>
+        <v>0.2272040648283469</v>
       </c>
       <c r="O36">
-        <v>0.2875379105224908</v>
+        <v>0.2314619984179024</v>
       </c>
       <c r="P36">
-        <v>0.3311753769798633</v>
+        <v>0.2889964619335157</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.03187119276478062</v>
+        <v>0.0334001456684439</v>
       </c>
       <c r="C37">
-        <v>0.06585828321729548</v>
+        <v>0.1402442068594625</v>
       </c>
       <c r="D37">
-        <v>0.09926286620612468</v>
+        <v>0.1016138945536741</v>
       </c>
       <c r="E37">
-        <v>0.0981932772797447</v>
+        <v>0.1388338602017827</v>
       </c>
       <c r="F37">
-        <v>0.1766102698328921</v>
+        <v>0.226281366102372</v>
       </c>
       <c r="G37">
-        <v>0.1835482507644713</v>
+        <v>0.3730491826307651</v>
       </c>
       <c r="H37">
-        <v>0.2139632013228229</v>
+        <v>0.385382511631263</v>
       </c>
       <c r="I37">
-        <v>0.2180358466298895</v>
+        <v>0.3964129829758797</v>
       </c>
       <c r="J37">
-        <v>0.2024581128141472</v>
+        <v>0.4152674222781796</v>
       </c>
       <c r="K37">
-        <v>0.2158272468204482</v>
+        <v>0.4152308769141115</v>
       </c>
       <c r="L37">
-        <v>0.222379830910585</v>
+        <v>0.4764789105325739</v>
       </c>
       <c r="M37">
-        <v>0.226230395910187</v>
+        <v>0.5088734259022658</v>
       </c>
       <c r="N37">
-        <v>0.2707586694395847</v>
+        <v>0.5355625051640305</v>
       </c>
       <c r="O37">
-        <v>0.2846394949107472</v>
+        <v>0.5492092506169851</v>
       </c>
       <c r="P37">
-        <v>0.3347014162590067</v>
+        <v>0.5694172421802788</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.03399377073933857</v>
+        <v>0.03172598854582903</v>
       </c>
       <c r="C38">
-        <v>0.06267578961722198</v>
+        <v>0.1248422337849036</v>
       </c>
       <c r="D38">
-        <v>0.09339385704762199</v>
+        <v>0.09127263588750645</v>
       </c>
       <c r="E38">
-        <v>0.09397651517734745</v>
+        <v>0.1369552649560696</v>
       </c>
       <c r="F38">
-        <v>0.1650413981570912</v>
+        <v>0.222363788560647</v>
       </c>
       <c r="G38">
-        <v>0.1745672336342255</v>
+        <v>0.232321248306154</v>
       </c>
       <c r="H38">
-        <v>0.2050145577627478</v>
+        <v>0.2478641785321933</v>
       </c>
       <c r="I38">
-        <v>0.2072639386730422</v>
+        <v>0.2618114582492795</v>
       </c>
       <c r="J38">
-        <v>0.1777725875385736</v>
+        <v>0.3095735005275949</v>
       </c>
       <c r="K38">
-        <v>0.205044923465792</v>
+        <v>0.3120714721716648</v>
       </c>
       <c r="L38">
-        <v>0.2107228019216631</v>
+        <v>0.3453745412010275</v>
       </c>
       <c r="M38">
-        <v>0.2143616729563306</v>
+        <v>0.3129029673067558</v>
       </c>
       <c r="N38">
-        <v>0.2518152208761429</v>
+        <v>0.3111457636087235</v>
       </c>
       <c r="O38">
-        <v>0.2666743369230101</v>
+        <v>0.3153631669119004</v>
       </c>
       <c r="P38">
-        <v>0.3180762597483678</v>
+        <v>0.3400444766012237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.02995914493010898</v>
+        <v>0.03116607819876061</v>
       </c>
       <c r="C39">
-        <v>0.05893832968637397</v>
+        <v>0.1180525282819783</v>
       </c>
       <c r="D39">
-        <v>0.09072597323931397</v>
+        <v>0.08754279101640605</v>
       </c>
       <c r="E39">
-        <v>0.09209587057783514</v>
+        <v>0.1354106900697701</v>
       </c>
       <c r="F39">
-        <v>0.1621754189104832</v>
+        <v>0.2074772788154148</v>
       </c>
       <c r="G39">
-        <v>0.1745373412972584</v>
+        <v>0.1902741554922169</v>
       </c>
       <c r="H39">
-        <v>0.2015560219326404</v>
+        <v>0.214590817723771</v>
       </c>
       <c r="I39">
-        <v>0.2043381034803005</v>
+        <v>0.2426916797942916</v>
       </c>
       <c r="J39">
-        <v>0.1857000751166109</v>
+        <v>0.2574247085472828</v>
       </c>
       <c r="K39">
-        <v>0.2050534800383627</v>
+        <v>0.2571251382518932</v>
       </c>
       <c r="L39">
-        <v>0.2104289528149184</v>
+        <v>0.2971251605179545</v>
       </c>
       <c r="M39">
-        <v>0.2111736553418373</v>
+        <v>0.2760197625563813</v>
       </c>
       <c r="N39">
-        <v>0.2485682108373041</v>
+        <v>0.2878577034355071</v>
       </c>
       <c r="O39">
-        <v>0.2684683719448139</v>
+        <v>0.2977653312148579</v>
       </c>
       <c r="P39">
-        <v>0.3121917511336004</v>
+        <v>0.3289590616205404</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.03090412997719943</v>
+        <v>0.03921796407271672</v>
       </c>
       <c r="C40">
-        <v>0.06111134942482105</v>
+        <v>0.07434696361875542</v>
       </c>
       <c r="D40">
-        <v>0.08857947186757253</v>
+        <v>0.07826171554938111</v>
       </c>
       <c r="E40">
-        <v>0.08978197164566942</v>
+        <v>0.1009401735491798</v>
       </c>
       <c r="F40">
-        <v>0.1640335868753259</v>
+        <v>0.1997084159955157</v>
       </c>
       <c r="G40">
-        <v>0.1727661121652653</v>
+        <v>0.2232986909914415</v>
       </c>
       <c r="H40">
-        <v>0.1961535673543797</v>
+        <v>0.2557755246226</v>
       </c>
       <c r="I40">
-        <v>0.2040100014774515</v>
+        <v>0.2932581125525346</v>
       </c>
       <c r="J40">
-        <v>0.1840050050251629</v>
+        <v>0.3429352259032636</v>
       </c>
       <c r="K40">
-        <v>0.2019383777956941</v>
+        <v>0.4010322985390266</v>
       </c>
       <c r="L40">
-        <v>0.1986187466556552</v>
+        <v>0.4102015180862841</v>
       </c>
       <c r="M40">
-        <v>0.1994646429688146</v>
+        <v>0.4253326808960284</v>
       </c>
       <c r="N40">
-        <v>0.2285299872403991</v>
+        <v>0.4388538667372491</v>
       </c>
       <c r="O40">
-        <v>0.2288492227209745</v>
+        <v>0.459684112417822</v>
       </c>
       <c r="P40">
-        <v>0.2901952807566707</v>
+        <v>0.5134791670877502</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.03238317433035665</v>
+        <v>0.05196500751688971</v>
       </c>
       <c r="C41">
-        <v>0.1344038312174641</v>
+        <v>0.08810526108949951</v>
       </c>
       <c r="D41">
-        <v>0.0984196287160497</v>
+        <v>0.1607019287811606</v>
       </c>
       <c r="E41">
-        <v>0.1368861308258309</v>
+        <v>0.2462686450619612</v>
       </c>
       <c r="F41">
-        <v>0.2343258365703572</v>
+        <v>0.3246046966911093</v>
       </c>
       <c r="G41">
-        <v>0.3758054057526184</v>
+        <v>0.392495045885672</v>
       </c>
       <c r="H41">
-        <v>0.3962471010206303</v>
+        <v>0.4298103640644135</v>
       </c>
       <c r="I41">
-        <v>0.4038913327669502</v>
+        <v>0.4684459644732635</v>
       </c>
       <c r="J41">
-        <v>0.4252143151446643</v>
+        <v>0.5015497234894305</v>
       </c>
       <c r="K41">
-        <v>0.4267203652410747</v>
+        <v>0.5945641244251266</v>
       </c>
       <c r="L41">
-        <v>0.4858414722659213</v>
+        <v>0.6533515789811908</v>
       </c>
       <c r="M41">
-        <v>0.5152287333759544</v>
+        <v>0.7007627258202155</v>
       </c>
       <c r="N41">
-        <v>0.5405386368515073</v>
+        <v>0.7588937705587544</v>
       </c>
       <c r="O41">
-        <v>0.5528768258494294</v>
+        <v>0.7983576529380273</v>
       </c>
       <c r="P41">
-        <v>0.5746402178281429</v>
+        <v>0.7926709545078318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.0300369427044308</v>
+        <v>0.0556953272533281</v>
       </c>
       <c r="C42">
-        <v>0.1249944240890825</v>
+        <v>0.06459063549897109</v>
       </c>
       <c r="D42">
-        <v>0.08956208199236698</v>
+        <v>0.1299700350988909</v>
       </c>
       <c r="E42">
-        <v>0.1373619670221743</v>
+        <v>0.2359958920762409</v>
       </c>
       <c r="F42">
-        <v>0.2269759516269975</v>
+        <v>0.3484160059042684</v>
       </c>
       <c r="G42">
-        <v>0.236048021965348</v>
+        <v>0.3563638285359321</v>
       </c>
       <c r="H42">
-        <v>0.2498594352955205</v>
+        <v>0.3817418408138696</v>
       </c>
       <c r="I42">
-        <v>0.2588566423621302</v>
+        <v>0.4259271071984533</v>
       </c>
       <c r="J42">
-        <v>0.3137618570787928</v>
+        <v>0.5294373382967502</v>
       </c>
       <c r="K42">
-        <v>0.3174944054700539</v>
+        <v>0.6128735350651319</v>
       </c>
       <c r="L42">
-        <v>0.3434115025997639</v>
+        <v>0.6536395112037688</v>
       </c>
       <c r="M42">
-        <v>0.3137879360148881</v>
+        <v>0.7259398180870873</v>
       </c>
       <c r="N42">
-        <v>0.3084503166445269</v>
+        <v>0.7692489850832058</v>
       </c>
       <c r="O42">
-        <v>0.3120169340455966</v>
+        <v>0.7698588066796783</v>
       </c>
       <c r="P42">
-        <v>0.3376320836710907</v>
+        <v>0.7648832510318918</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.03038244978037719</v>
+        <v>0.03822358740678949</v>
       </c>
       <c r="C43">
-        <v>0.1287074765120236</v>
+        <v>0.1042371776942294</v>
       </c>
       <c r="D43">
-        <v>0.08814799106977067</v>
+        <v>0.1678104809814149</v>
       </c>
       <c r="E43">
-        <v>0.141324811224853</v>
+        <v>0.2375267292347755</v>
       </c>
       <c r="F43">
-        <v>0.2163935600738122</v>
+        <v>0.3179880093007698</v>
       </c>
       <c r="G43">
-        <v>0.1998857136738815</v>
+        <v>0.3501737865972895</v>
       </c>
       <c r="H43">
-        <v>0.2199040556898692</v>
+        <v>0.3729762410695301</v>
       </c>
       <c r="I43">
-        <v>0.251846362583095</v>
+        <v>0.4078787058954588</v>
       </c>
       <c r="J43">
-        <v>0.2676691596673405</v>
+        <v>0.5152367771194292</v>
       </c>
       <c r="K43">
-        <v>0.2614383835597238</v>
+        <v>0.5396505869442585</v>
       </c>
       <c r="L43">
-        <v>0.3012801018643154</v>
+        <v>0.5732819641411777</v>
       </c>
       <c r="M43">
-        <v>0.2738412817351974</v>
+        <v>0.6182817520166648</v>
       </c>
       <c r="N43">
-        <v>0.2838270647374441</v>
+        <v>0.6201497131584794</v>
       </c>
       <c r="O43">
-        <v>0.2867152161724438</v>
+        <v>0.646312909761966</v>
       </c>
       <c r="P43">
-        <v>0.3146604469151844</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.03792603806362244</v>
-      </c>
-      <c r="C44">
-        <v>0.07360543491483107</v>
-      </c>
-      <c r="D44">
-        <v>0.07544923649138613</v>
-      </c>
-      <c r="E44">
-        <v>0.1010240425021064</v>
-      </c>
-      <c r="F44">
-        <v>0.2004603828790381</v>
-      </c>
-      <c r="G44">
-        <v>0.2251718663561245</v>
-      </c>
-      <c r="H44">
-        <v>0.2577481785345732</v>
-      </c>
-      <c r="I44">
-        <v>0.2956793233040897</v>
-      </c>
-      <c r="J44">
-        <v>0.3407748348092296</v>
-      </c>
-      <c r="K44">
-        <v>0.4001564232157109</v>
-      </c>
-      <c r="L44">
-        <v>0.408285855006883</v>
-      </c>
-      <c r="M44">
-        <v>0.4229661985985816</v>
-      </c>
-      <c r="N44">
-        <v>0.4360403767662712</v>
-      </c>
-      <c r="O44">
-        <v>0.4623750101553286</v>
-      </c>
-      <c r="P44">
-        <v>0.5154559869275672</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.05170095356738896</v>
-      </c>
-      <c r="C45">
-        <v>0.0861134574913473</v>
-      </c>
-      <c r="D45">
-        <v>0.1586761068469054</v>
-      </c>
-      <c r="E45">
-        <v>0.2407582448217383</v>
-      </c>
-      <c r="F45">
-        <v>0.3220268258673341</v>
-      </c>
-      <c r="G45">
-        <v>0.3881758543325844</v>
-      </c>
-      <c r="H45">
-        <v>0.4254400023386681</v>
-      </c>
-      <c r="I45">
-        <v>0.4633907311171301</v>
-      </c>
-      <c r="J45">
-        <v>0.4982467229479257</v>
-      </c>
-      <c r="K45">
-        <v>0.5888462939309613</v>
-      </c>
-      <c r="L45">
-        <v>0.6448964615527608</v>
-      </c>
-      <c r="M45">
-        <v>0.6830201303182596</v>
-      </c>
-      <c r="N45">
-        <v>0.7405649780096198</v>
-      </c>
-      <c r="O45">
-        <v>0.7837357051054079</v>
-      </c>
-      <c r="P45">
-        <v>0.7798215576025513</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.05478576587071798</v>
-      </c>
-      <c r="C46">
-        <v>0.06321591573972501</v>
-      </c>
-      <c r="D46">
-        <v>0.1270895562564752</v>
-      </c>
-      <c r="E46">
-        <v>0.2317329058615722</v>
-      </c>
-      <c r="F46">
-        <v>0.3423226980545122</v>
-      </c>
-      <c r="G46">
-        <v>0.3522052205574402</v>
-      </c>
-      <c r="H46">
-        <v>0.3775111380211604</v>
-      </c>
-      <c r="I46">
-        <v>0.4202719984035623</v>
-      </c>
-      <c r="J46">
-        <v>0.5174183589085182</v>
-      </c>
-      <c r="K46">
-        <v>0.6010797301545878</v>
-      </c>
-      <c r="L46">
-        <v>0.645373594834681</v>
-      </c>
-      <c r="M46">
-        <v>0.7170173361779578</v>
-      </c>
-      <c r="N46">
-        <v>0.7555444649642307</v>
-      </c>
-      <c r="O46">
-        <v>0.7516725591983349</v>
-      </c>
-      <c r="P46">
-        <v>0.7492535268976899</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.03742389974724009</v>
-      </c>
-      <c r="C47">
-        <v>0.1042725238419298</v>
-      </c>
-      <c r="D47">
-        <v>0.1657644515122551</v>
-      </c>
-      <c r="E47">
-        <v>0.2338965409278375</v>
-      </c>
-      <c r="F47">
-        <v>0.3153828679280637</v>
-      </c>
-      <c r="G47">
-        <v>0.3454134199146452</v>
-      </c>
-      <c r="H47">
-        <v>0.3623406984941953</v>
-      </c>
-      <c r="I47">
-        <v>0.3997393041587702</v>
-      </c>
-      <c r="J47">
-        <v>0.5067535526610714</v>
-      </c>
-      <c r="K47">
-        <v>0.5311676797920096</v>
-      </c>
-      <c r="L47">
-        <v>0.5635557067642939</v>
-      </c>
-      <c r="M47">
-        <v>0.6043872298568578</v>
-      </c>
-      <c r="N47">
-        <v>0.6070247920961522</v>
-      </c>
-      <c r="O47">
-        <v>0.6331493975221478</v>
-      </c>
-      <c r="P47">
-        <v>0.6545146878567367</v>
+        <v>0.6666053094516488</v>
       </c>
     </row>
   </sheetData>
